--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Pictures\kaspi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596F0CDF-DF71-4FE2-AA70-AC1DC04FEA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D516F395-14C2-4059-80C5-37AAEACFBB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$I$98</definedName>
   </definedNames>
   <calcPr calcId="140001"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="199">
   <si>
     <t>model</t>
   </si>
@@ -617,6 +617,15 @@
   </si>
   <si>
     <t>Nike Dunk Low Retro DD1391-103 men 9.5</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>color</t>
   </si>
 </sst>
 </file>
@@ -688,7 +697,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -740,15 +749,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -761,7 +761,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -794,20 +794,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1125,15 +1121,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G186"/>
-  <sheetFormatPr defaultColWidth="18.81640625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:I186"/>
+  <sheetFormatPr defaultColWidth="18.84375" defaultRowHeight="14.6"/>
   <cols>
-    <col min="2" max="2" width="59.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.1796875" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" style="17"/>
+    <col min="2" max="2" width="59.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="18.921875" customWidth="1"/>
+    <col min="6" max="6" width="28.15234375" customWidth="1"/>
+    <col min="7" max="7" width="18.84375" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1141,3593 +1138,4095 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>972999</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3">
         <v>25000</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2">
         <v>589715</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3">
         <v>25000</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="I3" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2">
         <v>950956</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3">
         <v>55000</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2">
         <v>785234</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3">
         <v>55000</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3">
         <v>55000</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="H6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3">
         <v>55000</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="H7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3">
         <v>55000</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="H8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3">
         <v>55000</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="H9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2">
         <v>309150</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3">
         <v>38000</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="I10" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2">
         <v>734002</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3">
         <v>25000</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2">
         <v>677390</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="3">
         <v>35000</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="H12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2">
         <v>677391</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3">
         <v>24000</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="H13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2">
         <v>677392</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="3">
         <v>26000</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="H14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2">
         <v>677393</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="3">
         <v>29000</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="H15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2">
         <v>677394</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="3">
         <v>33000</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="H16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2">
         <v>677395</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="3">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="3">
         <v>35000</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="H17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="3">
         <v>25000</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="I18" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="3">
         <v>27000</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="4">
         <v>508433</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="3">
         <v>38000</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="H20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="4">
         <v>265072</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="3">
         <v>38000</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="H21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="4">
         <v>911691</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="3">
         <v>38000</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="H22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="4">
         <v>138234</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="3">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="3">
         <v>38000</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="H23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="4">
         <v>362357</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="3">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="3">
         <v>38000</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="H24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="3">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="3">
         <v>27000</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="I25" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="4">
         <v>100005</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="3">
         <v>27000</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="I26" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="4">
         <v>100006</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="3">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="3">
         <v>39000</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="I27" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="4">
         <v>100007</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="3">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="3">
         <v>27000</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F28" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="I28" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="4">
         <v>100008</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="3">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="3">
         <v>27000</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="I29" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="4">
         <v>100003</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="3">
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="3">
         <v>27000</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="I30" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="3">
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="3">
         <v>27000</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="I31" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="4">
         <v>100001</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="3">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="3">
         <v>27000</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="I32" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="4">
         <v>100002</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="3">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="3">
         <v>27000</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F33" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="I33" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="4">
         <v>100004</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="3">
         <v>27000</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="H34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="I34" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="4">
         <v>100009</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="3">
         <v>59000</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="H35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="5">
         <v>100010</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="3">
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="3">
         <v>59000</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="H36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="4">
         <v>100011</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="3">
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="3">
         <v>59000</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="H37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="5">
         <v>100012</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="3">
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="3">
         <v>59000</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="H38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="4">
         <v>100013</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="3">
         <v>59000</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="H39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="4">
         <v>100014</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="3">
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="3">
         <v>59000</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="I40" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="4">
         <v>100015</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="3">
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="3">
         <v>46000</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="H41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="4">
         <v>100016</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="3">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="3">
         <v>46000</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="H42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="4">
         <v>100017</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="3">
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="3">
         <v>46000</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="H43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="4">
         <v>100018</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="3">
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="3">
         <v>46000</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="H44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="4">
         <v>100019</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="3">
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="3">
         <v>46000</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="H45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="4">
         <v>100020</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="3">
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="3">
         <v>46000</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="H46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="4"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="4"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="4"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="4"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="4"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="4"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="4"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="4"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="4"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="4"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="4"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="4"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="4"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="4"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="4"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="4"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="7">
         <v>100053</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D63" s="3">
+      <c r="G63" s="3">
         <v>60000</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F63" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="I63" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="7">
         <v>100054</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D64" s="3">
+      <c r="G64" s="3">
         <v>60000</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F64" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="H64" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="7">
         <v>100055</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D65" s="3">
+      <c r="G65" s="3">
         <v>60000</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="H65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="7">
         <v>100056</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D66" s="3">
+      <c r="G66" s="3">
         <v>60000</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F66" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="H66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="7">
         <v>100057</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D67" s="3">
+      <c r="G67" s="3">
         <v>60000</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F67" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="H67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="7">
         <v>100058</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D68" s="3">
+      <c r="G68" s="3">
         <v>60000</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F68" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="H68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="7">
         <v>100059</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D69" s="15">
+      <c r="G69" s="13">
         <v>80000</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="H69" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F69" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="I69" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="7">
         <v>100060</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="15">
+      <c r="G70" s="13">
         <v>80000</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F70" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="I70" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="7">
         <v>100061</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D71" s="3">
+      <c r="G71" s="3">
         <v>78000</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="H71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="7">
         <v>100062</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D72" s="15">
+      <c r="G72" s="13">
         <v>80000</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F72" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="I72" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="7">
         <v>100063</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D73" s="15">
+      <c r="G73" s="13">
         <v>67000</v>
       </c>
-      <c r="E73" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F73" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="H73" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="7">
         <v>100064</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D74" s="15">
+      <c r="G74" s="13">
         <v>67000</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="H74" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="4">
         <v>100029</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="3">
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" s="3">
         <v>44000</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F75" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="H75" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="4">
         <v>100030</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" s="3">
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76" s="3">
         <v>44000</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F76" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="H76" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="4">
         <v>100031</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D77" s="3">
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77" s="3">
         <v>44000</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F77" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="H77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="4">
         <v>100032</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D78" s="3">
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="3">
         <v>44000</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F78" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="H78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="4">
         <v>100033</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79" s="3">
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="3">
         <v>44000</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F79" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="H79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="4">
         <v>100034</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D80" s="3">
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80" s="3">
         <v>44000</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F80" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="H80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="4">
         <v>100035</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D81" s="3">
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81" s="3">
         <v>44000</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F81" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="H81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="4">
         <v>100036</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D82" s="3">
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="3">
         <v>44000</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F82" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="H82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="10">
         <v>100072</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D83" s="3">
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83" s="3">
         <v>44000</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="H83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="4">
         <v>100045</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D84" s="3">
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" s="3">
         <v>40000</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F84" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="H84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I84" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="4">
         <v>100046</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D85" s="3">
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G85" s="3">
         <v>40000</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F85" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="H85" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="4">
         <v>100047</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D86" s="3">
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G86" s="3">
         <v>40000</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="H86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="4">
         <v>100048</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D87" s="3">
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G87" s="3">
         <v>40000</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="H87" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="7">
         <v>100049</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" s="3">
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="3">
         <v>40000</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F88" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="H88" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" s="7">
         <v>100050</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D89" s="3">
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89" s="3">
         <v>40000</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F89" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="H89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="7">
         <v>100051</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" s="3">
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G90" s="3">
         <v>40000</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F90" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="H90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" s="7">
         <v>100052</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D91" s="3">
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="3">
         <v>40000</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F91" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="H91" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" s="7">
         <v>100071</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92" s="3">
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G92" s="3">
         <v>40000</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F92" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="H92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" s="7">
         <v>100065</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D93" s="3">
+      <c r="G93" s="3">
         <v>55600</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="H93" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F93" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="I93" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" s="7">
         <v>100066</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D94" s="3">
+      <c r="G94" s="3">
         <v>55600</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F94" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="H94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" s="7">
         <v>100067</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D95" s="3">
+      <c r="G95" s="3">
         <v>55600</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F95" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="H95" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" s="7">
         <v>100068</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D96" s="3">
+      <c r="G96" s="3">
         <v>55600</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F96" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="H96" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" s="7">
         <v>100069</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D97" s="3">
+      <c r="G97" s="3">
         <v>55600</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F97" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="H97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" s="7">
         <v>100070</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D98" s="3">
+      <c r="G98" s="3">
         <v>55600</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F98" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="H98" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" s="7">
         <v>100073</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D99" s="3">
+      <c r="G99" s="3">
         <v>42000</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="H99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" s="7">
         <v>100074</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D100" s="3">
+      <c r="G100" s="3">
         <v>42000</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F100" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="H100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" s="7">
         <v>100075</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D101" s="3">
+      <c r="G101" s="3">
         <v>42000</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F101" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="H101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" s="7">
         <v>100076</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D102" s="3">
+      <c r="G102" s="3">
         <v>42000</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F102" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="H102" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" s="7">
         <v>100077</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D103" s="3">
+      <c r="G103" s="3">
         <v>42000</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F103" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="H103" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" s="7">
         <v>100078</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D104" s="3">
+      <c r="G104" s="3">
         <v>42000</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F104" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="H104" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" s="7">
         <v>100079</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D105" s="3">
+      <c r="G105" s="3">
         <v>42000</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F105" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="H105" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" s="7">
         <v>100080</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D106" s="3">
+      <c r="G106" s="3">
         <v>42000</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F106" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="H106" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" s="7">
         <v>100081</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D107" s="3">
+      <c r="G107" s="3">
         <v>42000</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F107" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="H107" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" s="7">
         <v>100082</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D108" s="3">
+      <c r="G108" s="3">
         <v>42000</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F108" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="H108" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" s="7">
         <v>100083</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D109" s="3">
+      <c r="G109" s="3">
         <v>42000</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F109" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="H109" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" s="7">
         <v>100084</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D110" s="3">
+      <c r="G110" s="3">
         <v>42000</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F110" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="H110" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" s="7">
         <v>100085</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D111" s="3">
+      <c r="G111" s="3">
         <v>42000</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F111" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="H111" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" s="7">
         <v>100086</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D112" s="3">
+      <c r="G112" s="3">
         <v>42000</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F112" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="H112" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" s="7">
         <v>100087</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="11"/>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
+      <c r="F113" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D113" s="3">
+      <c r="G113" s="3">
         <v>42000</v>
       </c>
-      <c r="E113" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F113" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+      <c r="H113" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" s="7">
         <v>100088</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
+      <c r="F114" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D114" s="3">
+      <c r="G114" s="3">
         <v>42000</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F114" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+      <c r="H114" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" s="7">
         <v>100089</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="11"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
+      <c r="F115" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D115" s="3">
+      <c r="G115" s="3">
         <v>42000</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F115" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+      <c r="H115" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" s="7">
         <v>100090</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D116" s="3">
+      <c r="G116" s="3">
         <v>42000</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F116" s="1">
-        <v>14</v>
-      </c>
-      <c r="G116" s="12"/>
-    </row>
-    <row r="117" spans="1:7">
+      <c r="H116" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" s="7">
         <v>100091</v>
       </c>
       <c r="B117" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="11"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
+      <c r="F117" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D117" s="3">
+      <c r="G117" s="3">
         <v>42000</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F117" s="1">
-        <v>14</v>
-      </c>
-      <c r="G117" s="12"/>
-    </row>
-    <row r="118" spans="1:7">
+      <c r="H117" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" s="7">
         <v>100092</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
+      <c r="F118" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D118" s="3">
+      <c r="G118" s="3">
         <v>42000</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F118" s="1">
-        <v>14</v>
-      </c>
-      <c r="G118" s="12"/>
-    </row>
-    <row r="119" spans="1:7">
+      <c r="H118" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" s="7">
         <v>100093</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="11"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
+      <c r="F119" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D119" s="3">
+      <c r="G119" s="3">
         <v>42000</v>
       </c>
-      <c r="E119" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F119" s="1">
-        <v>14</v>
-      </c>
-      <c r="G119" s="12"/>
-    </row>
-    <row r="120" spans="1:7">
+      <c r="H119" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" s="7">
         <v>100094</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="11"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
+      <c r="F120" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D120" s="3">
+      <c r="G120" s="3">
         <v>42000</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F120" s="1">
-        <v>14</v>
-      </c>
-      <c r="G120" s="12"/>
-    </row>
-    <row r="121" spans="1:7">
+      <c r="H120" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" s="7">
         <v>100095</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="11"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
+      <c r="F121" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D121" s="3">
+      <c r="G121" s="3">
         <v>42000</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F121" s="1">
-        <v>14</v>
-      </c>
-      <c r="G121" s="12"/>
-    </row>
-    <row r="122" spans="1:7">
+      <c r="H121" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" s="7">
         <v>100096</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="11"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
+      <c r="F122" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D122" s="3">
+      <c r="G122" s="3">
         <v>42000</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F122" s="1">
-        <v>14</v>
-      </c>
-      <c r="G122" s="12"/>
-    </row>
-    <row r="123" spans="1:7">
+      <c r="H122" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" s="7">
         <v>100097</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="11"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
+      <c r="F123" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D123" s="3">
+      <c r="G123" s="3">
         <v>42000</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F123" s="1">
-        <v>14</v>
-      </c>
-      <c r="G123" s="12"/>
-    </row>
-    <row r="124" spans="1:7">
+      <c r="H123" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" s="7">
         <v>100098</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="11"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D124" s="3">
+      <c r="G124" s="3">
         <v>42000</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F124" s="1">
-        <v>14</v>
-      </c>
-      <c r="G124" s="12"/>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="H124" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" s="7">
         <v>100099</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="11"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D125" s="3">
+      <c r="G125" s="3">
         <v>42000</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F125" s="1">
-        <v>14</v>
-      </c>
-      <c r="G125" s="12"/>
-    </row>
-    <row r="126" spans="1:7">
+      <c r="H125" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" s="7">
         <v>100100</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="11"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D126" s="3">
+      <c r="G126" s="3">
         <v>42000</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F126" s="1">
-        <v>14</v>
-      </c>
-      <c r="G126" s="12"/>
-    </row>
-    <row r="127" spans="1:7">
+      <c r="H126" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" s="7">
         <v>100101</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D127" s="3">
+      <c r="G127" s="3">
         <v>42000</v>
       </c>
-      <c r="E127" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F127" s="1">
-        <v>14</v>
-      </c>
-      <c r="G127" s="12"/>
-    </row>
-    <row r="128" spans="1:7">
+      <c r="H127" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" s="7">
         <v>100102</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D128" s="3">
+      <c r="G128" s="3">
         <v>42000</v>
       </c>
-      <c r="E128" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F128" s="1">
-        <v>14</v>
-      </c>
-      <c r="G128" s="12"/>
-    </row>
-    <row r="129" spans="1:7">
+      <c r="H128" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" s="7">
         <v>100103</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D129" s="3">
+      <c r="G129" s="3">
         <v>42000</v>
       </c>
-      <c r="E129" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" s="1">
-        <v>14</v>
-      </c>
-      <c r="G129" s="12"/>
-    </row>
-    <row r="130" spans="1:7">
+      <c r="H129" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" s="7">
         <v>100104</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="11"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
+      <c r="F130" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D130" s="3">
+      <c r="G130" s="3">
         <v>42000</v>
       </c>
-      <c r="E130" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F130" s="1">
-        <v>14</v>
-      </c>
-      <c r="G130" s="12"/>
-    </row>
-    <row r="131" spans="1:7">
+      <c r="H130" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" s="7">
         <v>100105</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
+      <c r="F131" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D131" s="3">
+      <c r="G131" s="3">
         <v>42000</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F131" s="1">
-        <v>14</v>
-      </c>
-      <c r="G131" s="12"/>
-    </row>
-    <row r="132" spans="1:7">
+      <c r="H131" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" s="7">
         <v>100106</v>
       </c>
       <c r="B132" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D132" s="3">
+      <c r="G132" s="3">
         <v>42000</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F132" s="1">
-        <v>14</v>
-      </c>
-      <c r="G132" s="12"/>
-    </row>
-    <row r="133" spans="1:7">
+      <c r="H132" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" s="7">
         <v>100107</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D133" s="3">
+      <c r="G133" s="3">
         <v>42000</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F133" s="1">
-        <v>14</v>
-      </c>
-      <c r="G133" s="12"/>
-    </row>
-    <row r="134" spans="1:7">
+      <c r="H133" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" s="7">
         <v>100108</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="11"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
+      <c r="F134" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D134" s="3">
+      <c r="G134" s="3">
         <v>42000</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F134" s="1">
-        <v>14</v>
-      </c>
-      <c r="G134" s="12"/>
-    </row>
-    <row r="135" spans="1:7">
+      <c r="H134" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
       <c r="A135" s="7">
         <v>100109</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="11"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
+      <c r="F135" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D135" s="3">
+      <c r="G135" s="3">
         <v>323000</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F135" s="1">
-        <v>14</v>
-      </c>
-      <c r="G135" s="12"/>
-    </row>
-    <row r="136" spans="1:7">
+      <c r="H135" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" s="7">
         <v>100110</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C136" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D136" s="3">
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G136" s="3">
         <v>74000</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="H136" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F136" s="1">
-        <v>14</v>
-      </c>
-      <c r="G136" s="12"/>
-    </row>
-    <row r="137" spans="1:7">
+      <c r="I136" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" s="7">
         <v>100111</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C137" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D137" s="3">
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
+      <c r="F137" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G137" s="3">
         <v>77000</v>
       </c>
-      <c r="E137" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F137" s="1">
-        <v>14</v>
-      </c>
-      <c r="G137" s="12"/>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="H137" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" s="7">
         <v>100112</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C138" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" s="3">
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
+      <c r="F138" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G138" s="3">
         <v>77000</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F138" s="1">
-        <v>14</v>
-      </c>
-      <c r="G138" s="12"/>
-    </row>
-    <row r="139" spans="1:7">
+      <c r="H138" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" s="7">
         <v>100113</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C139" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D139" s="3">
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
+      <c r="F139" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G139" s="3">
         <v>77000</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F139" s="1">
-        <v>14</v>
-      </c>
-      <c r="G139" s="12"/>
-    </row>
-    <row r="140" spans="1:7">
+      <c r="H139" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" s="7">
         <v>100114</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C140" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D140" s="3">
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
+      <c r="F140" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G140" s="3">
         <v>77000</v>
       </c>
-      <c r="E140" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F140" s="1">
-        <v>14</v>
-      </c>
-      <c r="G140" s="12"/>
-    </row>
-    <row r="141" spans="1:7">
+      <c r="H140" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" s="7">
         <v>100115</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D141" s="3">
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
+      <c r="F141" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G141" s="3">
         <v>77000</v>
       </c>
-      <c r="E141" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F141" s="1">
-        <v>14</v>
-      </c>
-      <c r="G141" s="12"/>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="H141" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" s="7">
         <v>100116</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C142" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D142" s="3">
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G142" s="3">
         <v>77000</v>
       </c>
-      <c r="E142" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F142" s="1">
-        <v>14</v>
-      </c>
-      <c r="G142" s="12"/>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="H142" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" s="7">
         <v>100117</v>
       </c>
       <c r="B143" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C143" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D143" s="3">
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
+      <c r="F143" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G143" s="3">
         <v>77000</v>
       </c>
-      <c r="E143" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F143" s="1">
-        <v>14</v>
-      </c>
-      <c r="G143" s="12"/>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="H143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" s="7">
         <v>100118</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C144" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D144" s="3">
+      <c r="C144" s="11"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G144" s="3">
         <v>77000</v>
       </c>
-      <c r="E144" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F144" s="1">
-        <v>14</v>
-      </c>
-      <c r="G144" s="12"/>
-    </row>
-    <row r="145" spans="1:7">
+      <c r="H144" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" s="7">
         <v>100119</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C145" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D145" s="3">
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G145" s="3">
         <v>77000</v>
       </c>
-      <c r="E145" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F145" s="13">
-        <v>14</v>
-      </c>
-      <c r="G145" s="14"/>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="H145" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" s="7">
         <v>100120</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C146" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D146" s="15">
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G146" s="13">
         <v>80000</v>
       </c>
-      <c r="E146" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F146" s="13">
-        <v>14</v>
-      </c>
-      <c r="G146" s="14"/>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="H146" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" s="7">
         <v>100121</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C147" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D147" s="15">
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G147" s="13">
         <v>80000</v>
       </c>
-      <c r="E147" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F147" s="13">
-        <v>14</v>
-      </c>
-      <c r="G147" s="14"/>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="H147" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" s="7">
         <v>100122</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C148" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D148" s="15">
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G148" s="13">
         <v>80000</v>
       </c>
-      <c r="E148" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F148" s="13">
-        <v>14</v>
-      </c>
-      <c r="G148" s="14"/>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="H148" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" s="7">
         <v>100123</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C149" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D149" s="15">
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
+      <c r="F149" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G149" s="13">
         <v>91000</v>
       </c>
-      <c r="E149" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F149" s="13">
-        <v>14</v>
-      </c>
-      <c r="G149" s="14"/>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="H149" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" s="7">
         <v>100124</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C150" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D150" s="15">
+      <c r="C150" s="11"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G150" s="13">
         <v>91000</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F150" s="13">
-        <v>14</v>
-      </c>
-      <c r="G150" s="14"/>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="H150" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" s="7">
         <v>100125</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C151" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D151" s="15">
+      <c r="C151" s="11"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11"/>
+      <c r="F151" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G151" s="13">
         <v>91000</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="H151" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F151" s="13">
-        <v>14</v>
-      </c>
-      <c r="G151" s="14"/>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="I151" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" s="7">
         <v>100126</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C152" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D152" s="15">
+      <c r="C152" s="11"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
+      <c r="F152" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G152" s="13">
         <v>91000</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="H152" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F152" s="13">
-        <v>14</v>
-      </c>
-      <c r="G152" s="14"/>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="I152" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" s="7">
         <v>100127</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C153" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D153" s="15">
+      <c r="C153" s="11"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G153" s="13">
         <v>91000</v>
       </c>
-      <c r="E153" s="2" t="s">
+      <c r="H153" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F153" s="13">
-        <v>14</v>
-      </c>
-      <c r="G153" s="14"/>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="I153" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" s="7">
         <v>100128</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D154" s="15">
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G154" s="13">
         <v>67000</v>
       </c>
-      <c r="E154" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F154" s="13">
-        <v>14</v>
-      </c>
-      <c r="G154" s="14"/>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="H154" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" s="7">
         <v>100129</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D155" s="15">
+      <c r="C155" s="11"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G155" s="13">
         <v>67000</v>
       </c>
-      <c r="E155" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F155" s="13">
-        <v>14</v>
-      </c>
-      <c r="G155" s="14"/>
-    </row>
-    <row r="156" spans="1:7">
+      <c r="H155" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" s="7">
         <v>100130</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D156" s="15">
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G156" s="13">
         <v>67000</v>
       </c>
-      <c r="E156" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F156" s="13">
-        <v>14</v>
-      </c>
-      <c r="G156" s="14"/>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="H156" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" s="7">
         <v>100131</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C157" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D157" s="15">
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G157" s="13">
         <v>67000</v>
       </c>
-      <c r="E157" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F157" s="13">
-        <v>14</v>
-      </c>
-      <c r="G157" s="14"/>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="H157" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" s="7">
         <v>100132</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C158" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D158" s="15">
+      <c r="C158" s="11"/>
+      <c r="D158" s="11"/>
+      <c r="E158" s="11"/>
+      <c r="F158" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G158" s="13">
         <v>76000</v>
       </c>
-      <c r="E158" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F158" s="13">
-        <v>14</v>
-      </c>
-      <c r="G158" s="14"/>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="H158" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" s="7">
         <v>100133</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C159" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D159" s="15">
+      <c r="C159" s="11"/>
+      <c r="D159" s="11"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G159" s="13">
         <v>80000</v>
       </c>
-      <c r="E159" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F159" s="13">
-        <v>14</v>
-      </c>
-      <c r="G159" s="14"/>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="H159" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" s="7">
         <v>100134</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C160" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D160" s="15">
+      <c r="C160" s="11"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G160" s="13">
         <v>80000</v>
       </c>
-      <c r="E160" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F160" s="13">
-        <v>14</v>
-      </c>
-      <c r="G160" s="14"/>
-    </row>
-    <row r="161" spans="1:7">
+      <c r="H160" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" s="7">
         <v>100135</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C161" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D161" s="15">
+      <c r="C161" s="11"/>
+      <c r="D161" s="11"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G161" s="13">
         <v>80000</v>
       </c>
-      <c r="E161" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F161" s="13">
-        <v>14</v>
-      </c>
-      <c r="G161" s="14"/>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="H161" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" s="7">
         <v>100158</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="C162" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D162" s="15">
+      <c r="C162" s="11"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G162" s="13">
         <v>80000</v>
       </c>
-      <c r="E162" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F162" s="13">
-        <v>14</v>
-      </c>
-      <c r="G162" s="14"/>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="H162" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" s="7">
         <v>100159</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C163" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D163" s="15">
+      <c r="C163" s="11"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G163" s="13">
         <v>80000</v>
       </c>
-      <c r="E163" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F163" s="13">
-        <v>14</v>
-      </c>
-      <c r="G163" s="14"/>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="H163" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" s="7">
         <v>100160</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C164" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D164" s="15">
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G164" s="13">
         <v>80000</v>
       </c>
-      <c r="E164" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F164" s="13">
-        <v>14</v>
-      </c>
-      <c r="G164" s="14"/>
-    </row>
-    <row r="165" spans="1:7">
+      <c r="H164" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165" s="7">
         <v>100161</v>
       </c>
       <c r="B165" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D165" s="15">
+      <c r="C165" s="11"/>
+      <c r="D165" s="11"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G165" s="13">
         <v>80000</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F165" s="13">
-        <v>14</v>
-      </c>
-      <c r="G165" s="14"/>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="H165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" s="7">
         <v>100162</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D166" s="15">
+      <c r="C166" s="11"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G166" s="13">
         <v>80000</v>
       </c>
-      <c r="E166" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F166" s="13">
-        <v>14</v>
-      </c>
-      <c r="G166" s="14"/>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="H166" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
       <c r="A167" s="7">
         <v>100163</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C167" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D167" s="15">
+      <c r="C167" s="11"/>
+      <c r="D167" s="11"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G167" s="13">
         <v>80000</v>
       </c>
-      <c r="E167" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F167" s="13">
-        <v>14</v>
-      </c>
-      <c r="G167" s="14"/>
-    </row>
-    <row r="168" spans="1:7">
+      <c r="H167" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
       <c r="A168" s="7">
         <v>100164</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C168" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D168" s="15">
+      <c r="C168" s="11"/>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G168" s="13">
         <v>80000</v>
       </c>
-      <c r="E168" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F168" s="13">
-        <v>14</v>
-      </c>
-      <c r="G168" s="14"/>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="H168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169" s="7">
         <v>100165</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C169" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D169" s="15">
+      <c r="C169" s="11"/>
+      <c r="D169" s="11"/>
+      <c r="E169" s="11"/>
+      <c r="F169" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G169" s="13">
         <v>80000</v>
       </c>
-      <c r="E169" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F169" s="13">
-        <v>14</v>
-      </c>
-      <c r="G169" s="14"/>
-    </row>
-    <row r="170" spans="1:7">
+      <c r="H169" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
       <c r="A170" s="7">
         <v>100152</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C170" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D170" s="15">
+      <c r="C170" s="11"/>
+      <c r="D170" s="11"/>
+      <c r="E170" s="11"/>
+      <c r="F170" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G170" s="13">
         <v>74000</v>
       </c>
-      <c r="E170" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F170" s="13">
-        <v>14</v>
-      </c>
-      <c r="G170" s="14"/>
-    </row>
-    <row r="171" spans="1:7">
+      <c r="H170" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" s="7">
         <v>100153</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C171" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D171" s="15">
+      <c r="C171" s="11"/>
+      <c r="D171" s="11"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G171" s="13">
         <v>74000</v>
       </c>
-      <c r="E171" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F171" s="13">
-        <v>14</v>
-      </c>
-      <c r="G171" s="14"/>
-    </row>
-    <row r="172" spans="1:7">
+      <c r="H171" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" s="7">
         <v>100154</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C172" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D172" s="15">
+      <c r="C172" s="11"/>
+      <c r="D172" s="11"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G172" s="13">
         <v>74000</v>
       </c>
-      <c r="E172" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F172" s="13">
-        <v>14</v>
-      </c>
-      <c r="G172" s="14"/>
-    </row>
-    <row r="173" spans="1:7">
+      <c r="H172" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" s="7">
         <v>100155</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C173" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D173" s="15">
+      <c r="C173" s="11"/>
+      <c r="D173" s="11"/>
+      <c r="E173" s="11"/>
+      <c r="F173" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G173" s="13">
         <v>74000</v>
       </c>
-      <c r="E173" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F173" s="13">
-        <v>14</v>
-      </c>
-      <c r="G173" s="14"/>
-    </row>
-    <row r="174" spans="1:7">
+      <c r="H173" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" s="7">
         <v>100156</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C174" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D174" s="15">
+      <c r="C174" s="11"/>
+      <c r="D174" s="11"/>
+      <c r="E174" s="11"/>
+      <c r="F174" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G174" s="13">
         <v>74000</v>
       </c>
-      <c r="E174" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F174" s="13">
-        <v>14</v>
-      </c>
-      <c r="G174" s="14"/>
-    </row>
-    <row r="175" spans="1:7">
+      <c r="H174" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" s="7">
         <v>100157</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C175" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D175" s="15">
+      <c r="C175" s="11"/>
+      <c r="D175" s="11"/>
+      <c r="E175" s="11"/>
+      <c r="F175" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G175" s="13">
         <v>74000</v>
       </c>
-      <c r="E175" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F175" s="13">
-        <v>14</v>
-      </c>
-      <c r="G175" s="14"/>
-    </row>
-    <row r="176" spans="1:7">
+      <c r="H175" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" s="7">
         <v>100150</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C176" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D176" s="15">
+      <c r="C176" s="11"/>
+      <c r="D176" s="11"/>
+      <c r="E176" s="11"/>
+      <c r="F176" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G176" s="13">
         <v>74000</v>
       </c>
-      <c r="E176" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F176" s="13">
-        <v>14</v>
-      </c>
-      <c r="G176" s="14"/>
-    </row>
-    <row r="177" spans="1:7">
+      <c r="H176" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" s="7">
         <v>100151</v>
       </c>
       <c r="B177" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C177" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D177" s="15">
+      <c r="C177" s="11"/>
+      <c r="D177" s="11"/>
+      <c r="E177" s="11"/>
+      <c r="F177" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G177" s="13">
         <v>74000</v>
       </c>
-      <c r="E177" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F177" s="13">
-        <v>14</v>
-      </c>
-      <c r="G177" s="14"/>
-    </row>
-    <row r="178" spans="1:7">
+      <c r="H177" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" s="7">
         <v>100167</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D178" s="15">
+      <c r="C178" s="11"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G178" s="13">
         <v>124000</v>
       </c>
-      <c r="E178" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F178" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
+      <c r="H178" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" s="7">
         <v>100168</v>
       </c>
       <c r="B179" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C179" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D179" s="15">
+      <c r="C179" s="11"/>
+      <c r="D179" s="11"/>
+      <c r="E179" s="11"/>
+      <c r="F179" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G179" s="13">
         <v>124000</v>
       </c>
-      <c r="E179" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F179" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
+      <c r="H179" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" s="7">
         <v>100169</v>
       </c>
       <c r="B180" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C180" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D180" s="15">
+      <c r="C180" s="11"/>
+      <c r="D180" s="11"/>
+      <c r="E180" s="11"/>
+      <c r="F180" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G180" s="13">
         <v>124000</v>
       </c>
-      <c r="E180" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F180" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
+      <c r="H180" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" s="7">
         <v>100166</v>
       </c>
       <c r="B181" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C181" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D181" s="15">
+      <c r="C181" s="11"/>
+      <c r="D181" s="11"/>
+      <c r="E181" s="11"/>
+      <c r="F181" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G181" s="13">
         <v>124000</v>
       </c>
-      <c r="E181" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F181" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
+      <c r="H181" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" s="7">
         <v>100170</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C182" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D182" s="15">
+      <c r="C182" s="11"/>
+      <c r="D182" s="11"/>
+      <c r="E182" s="11"/>
+      <c r="F182" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G182" s="13">
         <v>110000</v>
       </c>
-      <c r="E182" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F182" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
+      <c r="H182" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" s="7">
         <v>100171</v>
       </c>
       <c r="B183" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C183" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D183" s="15">
+      <c r="C183" s="11"/>
+      <c r="D183" s="11"/>
+      <c r="E183" s="11"/>
+      <c r="F183" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G183" s="13">
         <v>110000</v>
       </c>
-      <c r="E183" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F183" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
+      <c r="H183" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" s="7">
         <v>100172</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C184" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D184" s="15">
+      <c r="C184" s="11"/>
+      <c r="D184" s="11"/>
+      <c r="E184" s="11"/>
+      <c r="F184" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G184" s="13">
         <v>110000</v>
       </c>
-      <c r="E184" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F184" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
+      <c r="H184" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" s="7">
         <v>100165</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C185" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D185" s="15">
+      <c r="C185" s="11"/>
+      <c r="D185" s="11"/>
+      <c r="E185" s="11"/>
+      <c r="F185" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G185" s="13">
         <v>110000</v>
       </c>
-      <c r="E185" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F185" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
+      <c r="H185" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" s="7">
         <v>100175</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C186" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D186" s="16">
+      <c r="C186" s="11"/>
+      <c r="D186" s="11"/>
+      <c r="E186" s="11"/>
+      <c r="F186" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G186" s="13">
         <v>56000</v>
       </c>
-      <c r="E186" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F186" s="1">
+      <c r="H186" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" s="1">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F98" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I98" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Ошибка" error="Длина строки превышает допустимое значение!" sqref="B63:B74 B93:B98" xr:uid="{A1013F27-C731-45DC-A196-0A10BBAF090D}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" showErrorMessage="1" errorTitle="Ошибка" error="Длина строки превышает допустимое значение!" sqref="B63:E74 B93:E98" xr:uid="{A1013F27-C731-45DC-A196-0A10BBAF090D}">
       <formula1>255</formula1>
     </dataValidation>
   </dataValidations>
@@ -4744,10 +5243,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="136.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="136.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C0699-8A4F-473C-880F-3A371C55AD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A738E4-A9BC-4E3E-B202-8B26BC98F07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -219,15 +219,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -567,13 +564,13 @@
       <c r="G1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -599,7 +596,9 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
@@ -615,7 +614,9 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
@@ -631,7 +632,9 @@
       <c r="G4" s="1">
         <v>3</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
@@ -647,7 +650,9 @@
       <c r="G5" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
@@ -663,7 +668,9 @@
       <c r="G6" s="1">
         <v>5</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
@@ -679,7 +686,9 @@
       <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
@@ -693,7 +702,9 @@
       <c r="G8" s="1">
         <v>7</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
@@ -709,7 +720,9 @@
       <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
@@ -723,7 +736,9 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
@@ -737,7 +752,9 @@
       <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -751,7 +768,9 @@
       <c r="G12" s="1">
         <v>4</v>
       </c>
-      <c r="H12" s="3"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
@@ -765,7 +784,9 @@
       <c r="G13" s="1">
         <v>5</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
@@ -779,7 +800,9 @@
       <c r="G14" s="1">
         <v>6</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
@@ -793,7 +816,9 @@
       <c r="G15" s="1">
         <v>7</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -837,13 +862,13 @@
       <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -869,6 +894,9 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
@@ -884,6 +912,9 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
@@ -899,6 +930,9 @@
       <c r="G4" s="1">
         <v>3</v>
       </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
@@ -914,6 +948,9 @@
       <c r="G5" s="1">
         <v>4</v>
       </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
@@ -929,6 +966,9 @@
       <c r="G6" s="1">
         <v>5</v>
       </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
@@ -944,6 +984,9 @@
       <c r="G7" s="1">
         <v>6</v>
       </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
@@ -957,6 +1000,9 @@
       <c r="G8" s="1">
         <v>7</v>
       </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
@@ -972,6 +1018,9 @@
       <c r="G9" s="1">
         <v>1</v>
       </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
@@ -985,6 +1034,9 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
@@ -998,6 +1050,9 @@
       <c r="G11" s="1">
         <v>3</v>
       </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -1011,6 +1066,9 @@
       <c r="G12" s="1">
         <v>4</v>
       </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
@@ -1024,6 +1082,9 @@
       <c r="G13" s="1">
         <v>5</v>
       </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
@@ -1037,6 +1098,9 @@
       <c r="G14" s="1">
         <v>6</v>
       </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
@@ -1050,8 +1114,23 @@
       <c r="G15" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>500101</v>
       </c>
@@ -1073,8 +1152,11 @@
       <c r="G17" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>500102</v>
       </c>
@@ -1088,8 +1170,11 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>500103</v>
       </c>
@@ -1103,8 +1188,11 @@
       <c r="G19" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>500104</v>
       </c>
@@ -1118,8 +1206,11 @@
       <c r="G20" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>500105</v>
       </c>
@@ -1133,8 +1224,11 @@
       <c r="G21" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>500106</v>
       </c>
@@ -1148,8 +1242,11 @@
       <c r="G22" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>500107</v>
       </c>
@@ -1161,8 +1258,11 @@
       <c r="G23" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>500108</v>
       </c>
@@ -1174,13 +1274,25 @@
       <c r="G24" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="G25" s="2">
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>500201</v>
       </c>
@@ -1202,8 +1314,11 @@
       <c r="G26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>500202</v>
       </c>
@@ -1217,8 +1332,11 @@
       <c r="G27" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>500203</v>
       </c>
@@ -1232,8 +1350,11 @@
       <c r="G28" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>500204</v>
       </c>
@@ -1247,8 +1368,11 @@
       <c r="G29" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>500205</v>
       </c>
@@ -1260,8 +1384,11 @@
       <c r="G30" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>500206</v>
       </c>
@@ -1273,8 +1400,11 @@
       <c r="G31" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>500207</v>
       </c>
@@ -1286,8 +1416,11 @@
       <c r="G32" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>500208</v>
       </c>
@@ -1299,6 +1432,9 @@
       <c r="G33" s="1">
         <v>8</v>
       </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A738E4-A9BC-4E3E-B202-8B26BC98F07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA7375F-10E3-4945-A6A2-13248A23BB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
   <si>
     <t>model</t>
   </si>
@@ -58,9 +58,6 @@
     <t>color</t>
   </si>
   <si>
-    <t>size</t>
-  </si>
-  <si>
     <t>sku</t>
   </si>
   <si>
@@ -73,24 +70,6 @@
     <t>image</t>
   </si>
   <si>
-    <t>100001_1</t>
-  </si>
-  <si>
-    <t>100001_2</t>
-  </si>
-  <si>
-    <t>100001_3</t>
-  </si>
-  <si>
-    <t>100001_4</t>
-  </si>
-  <si>
-    <t>100001_5</t>
-  </si>
-  <si>
-    <t>100001_6</t>
-  </si>
-  <si>
     <t>grey</t>
   </si>
   <si>
@@ -161,6 +140,9 @@
   </si>
   <si>
     <t>size EU</t>
+  </si>
+  <si>
+    <t>100001_1, 100001_2, 100001_3</t>
   </si>
 </sst>
 </file>
@@ -544,7 +526,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -559,13 +541,13 @@
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -582,7 +564,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -591,7 +573,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -608,9 +590,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="1">
         <v>2</v>
       </c>
@@ -626,9 +606,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="1">
         <v>3</v>
       </c>
@@ -644,9 +622,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1">
         <v>4</v>
       </c>
@@ -662,9 +638,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="1">
         <v>5</v>
       </c>
@@ -680,9 +654,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1">
         <v>6</v>
       </c>
@@ -714,7 +686,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1">
@@ -842,7 +814,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -857,13 +829,13 @@
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -880,16 +852,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -907,7 +879,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -925,7 +897,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -943,7 +915,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
@@ -961,7 +933,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -979,7 +951,7 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
@@ -1012,7 +984,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1">
@@ -1138,16 +1110,16 @@
         <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -1165,7 +1137,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G18" s="1">
         <v>2</v>
@@ -1183,7 +1155,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1">
         <v>3</v>
@@ -1201,7 +1173,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G20" s="1">
         <v>4</v>
@@ -1219,7 +1191,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G21" s="1">
         <v>5</v>
@@ -1237,7 +1209,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G22" s="1">
         <v>6</v>
@@ -1300,16 +1272,16 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -1327,7 +1299,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G27" s="1">
         <v>2</v>
@@ -1345,7 +1317,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G28" s="1">
         <v>3</v>
@@ -1363,7 +1335,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G29" s="1">
         <v>4</v>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA7375F-10E3-4945-A6A2-13248A23BB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78A2E05-7C62-44A7-9F42-E4AF396D0383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>model</t>
   </si>
@@ -73,54 +73,6 @@
     <t>grey</t>
   </si>
   <si>
-    <t>500001_1</t>
-  </si>
-  <si>
-    <t>500001_2</t>
-  </si>
-  <si>
-    <t>500001_3</t>
-  </si>
-  <si>
-    <t>500001_4</t>
-  </si>
-  <si>
-    <t>500001_5</t>
-  </si>
-  <si>
-    <t>500001_6</t>
-  </si>
-  <si>
-    <t>500100_1</t>
-  </si>
-  <si>
-    <t>500100_2</t>
-  </si>
-  <si>
-    <t>500100_3</t>
-  </si>
-  <si>
-    <t>500100_4</t>
-  </si>
-  <si>
-    <t>500100_5</t>
-  </si>
-  <si>
-    <t>500100_6</t>
-  </si>
-  <si>
-    <t>500201_1</t>
-  </si>
-  <si>
-    <t>500201_2</t>
-  </si>
-  <si>
-    <t>500201_3</t>
-  </si>
-  <si>
-    <t>500201_4</t>
-  </si>
-  <si>
     <t>white green</t>
   </si>
   <si>
@@ -142,7 +94,16 @@
     <t>size EU</t>
   </si>
   <si>
-    <t>100001_1, 100001_2, 100001_3</t>
+    <t>100001_1 100001_2 100001_3</t>
+  </si>
+  <si>
+    <t>500001_1 500001_2 500001_3</t>
+  </si>
+  <si>
+    <t>500100_1 500100_2 500100_3</t>
+  </si>
+  <si>
+    <t>500201_1 500201_2 500201_3</t>
   </si>
 </sst>
 </file>
@@ -544,10 +505,10 @@
         <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -573,7 +534,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -832,10 +793,10 @@
         <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -852,7 +813,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -861,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -878,9 +839,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="1">
         <v>2</v>
       </c>
@@ -896,9 +855,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="1">
         <v>3</v>
       </c>
@@ -914,9 +871,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1">
         <v>4</v>
       </c>
@@ -932,9 +887,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="1">
         <v>5</v>
       </c>
@@ -950,9 +903,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1">
         <v>6</v>
       </c>
@@ -1110,16 +1061,16 @@
         <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -1136,9 +1087,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F18" s="1"/>
       <c r="G18" s="1">
         <v>2</v>
       </c>
@@ -1154,9 +1103,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="F19" s="1"/>
       <c r="G19" s="1">
         <v>3</v>
       </c>
@@ -1172,9 +1119,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="F20" s="1"/>
       <c r="G20" s="1">
         <v>4</v>
       </c>
@@ -1190,9 +1135,7 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="F21" s="1"/>
       <c r="G21" s="1">
         <v>5</v>
       </c>
@@ -1208,9 +1151,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="F22" s="1"/>
       <c r="G22" s="1">
         <v>6</v>
       </c>
@@ -1272,16 +1213,16 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -1298,9 +1239,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="F27" s="1"/>
       <c r="G27" s="1">
         <v>2</v>
       </c>
@@ -1316,9 +1255,7 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="F28" s="1"/>
       <c r="G28" s="1">
         <v>3</v>
       </c>
@@ -1334,9 +1271,7 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="F29" s="1"/>
       <c r="G29" s="1">
         <v>4</v>
       </c>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78A2E05-7C62-44A7-9F42-E4AF396D0383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836A3B43-2D68-430D-9EB6-E2B8265C8C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="27">
   <si>
     <t>model</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>500201_1 500201_2 500201_3</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -474,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50E1A44-280D-4411-9C01-14D3EB718FB5}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -485,7 +488,7 @@
     <col min="9" max="16384" width="9.23046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -516,8 +519,11 @@
       <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
@@ -542,8 +548,11 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>100002</v>
       </c>
@@ -558,8 +567,11 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>100003</v>
       </c>
@@ -574,8 +586,11 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>100004</v>
       </c>
@@ -590,8 +605,11 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>100005</v>
       </c>
@@ -606,8 +624,11 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>100006</v>
       </c>
@@ -622,8 +643,11 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>100007</v>
       </c>
@@ -638,8 +662,11 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>100008</v>
       </c>
@@ -656,8 +683,11 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>100009</v>
       </c>
@@ -672,8 +702,11 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>100010</v>
       </c>
@@ -688,8 +721,11 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>100011</v>
       </c>
@@ -704,8 +740,11 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>100012</v>
       </c>
@@ -720,8 +759,11 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>100013</v>
       </c>
@@ -736,8 +778,11 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>100014</v>
       </c>
@@ -752,6 +797,9 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -761,7 +809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC76538-67CE-4574-A08C-7F9575FC0AF6}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -773,7 +821,7 @@
     <col min="8" max="16384" width="9.23046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -804,8 +852,11 @@
       <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>500001</v>
       </c>
@@ -830,8 +881,11 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>500002</v>
       </c>
@@ -846,8 +900,11 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>500003</v>
       </c>
@@ -862,8 +919,11 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>500004</v>
       </c>
@@ -878,8 +938,11 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>500005</v>
       </c>
@@ -894,8 +957,11 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>500006</v>
       </c>
@@ -910,8 +976,11 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>500007</v>
       </c>
@@ -926,8 +995,11 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>500008</v>
       </c>
@@ -944,8 +1016,11 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>500009</v>
       </c>
@@ -960,8 +1035,11 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>500010</v>
       </c>
@@ -976,8 +1054,11 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>500011</v>
       </c>
@@ -992,8 +1073,11 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>500012</v>
       </c>
@@ -1008,8 +1092,11 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>500013</v>
       </c>
@@ -1024,8 +1111,11 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>500014</v>
       </c>
@@ -1040,8 +1130,11 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1052,8 +1145,11 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K16" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>500101</v>
       </c>
@@ -1078,8 +1174,11 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>500102</v>
       </c>
@@ -1094,8 +1193,11 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K18" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>500103</v>
       </c>
@@ -1110,8 +1212,11 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>500104</v>
       </c>
@@ -1126,8 +1231,11 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>500105</v>
       </c>
@@ -1142,8 +1250,11 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>500106</v>
       </c>
@@ -1158,8 +1269,11 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K22" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>500107</v>
       </c>
@@ -1174,8 +1288,11 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K23" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>500108</v>
       </c>
@@ -1190,8 +1307,11 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1204,8 +1324,11 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K25" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>500201</v>
       </c>
@@ -1230,8 +1353,11 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K26" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>500202</v>
       </c>
@@ -1246,8 +1372,11 @@
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>500203</v>
       </c>
@@ -1262,8 +1391,11 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>500204</v>
       </c>
@@ -1278,8 +1410,11 @@
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>500205</v>
       </c>
@@ -1294,8 +1429,11 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K30" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>500206</v>
       </c>
@@ -1310,8 +1448,11 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K31" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>500207</v>
       </c>
@@ -1326,8 +1467,11 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K32" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>500208</v>
       </c>
@@ -1342,6 +1486,9 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836A3B43-2D68-430D-9EB6-E2B8265C8C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870F8BEA-70D8-4FC7-8F27-5EAFD62637F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="28">
   <si>
     <t>model</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>500008_1 500008_2 500008_3</t>
   </si>
 </sst>
 </file>
@@ -546,7 +549,9 @@
         <v>1</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1">
+        <v>50000</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
         <v>26</v>
@@ -565,7 +570,9 @@
         <v>2</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1">
+        <v>50000</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
         <v>26</v>
@@ -584,7 +591,9 @@
         <v>3</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>50000</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
         <v>26</v>
@@ -603,7 +612,9 @@
         <v>4</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <v>50000</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
         <v>26</v>
@@ -622,7 +633,9 @@
         <v>5</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>50000</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
         <v>26</v>
@@ -641,7 +654,9 @@
         <v>6</v>
       </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>50000</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
         <v>26</v>
@@ -660,7 +675,9 @@
         <v>7</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>50000</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
         <v>26</v>
@@ -681,7 +698,9 @@
         <v>1</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>50000</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
         <v>26</v>
@@ -700,7 +719,9 @@
         <v>2</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>50000</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
         <v>26</v>
@@ -719,7 +740,9 @@
         <v>3</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>50000</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
         <v>26</v>
@@ -738,7 +761,9 @@
         <v>4</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>50000</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
         <v>26</v>
@@ -757,7 +782,9 @@
         <v>5</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>50000</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
         <v>26</v>
@@ -776,7 +803,9 @@
         <v>6</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>50000</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
         <v>26</v>
@@ -795,7 +824,9 @@
         <v>7</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>50000</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
         <v>26</v>
@@ -879,7 +910,9 @@
         <v>1</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1">
+        <v>60000</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
         <v>26</v>
@@ -898,7 +931,9 @@
         <v>2</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1">
+        <v>60000</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
         <v>26</v>
@@ -917,7 +952,9 @@
         <v>3</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>60000</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
         <v>26</v>
@@ -936,7 +973,9 @@
         <v>4</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <v>60000</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
         <v>26</v>
@@ -955,7 +994,9 @@
         <v>5</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>60000</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
         <v>26</v>
@@ -974,7 +1015,9 @@
         <v>6</v>
       </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>60000</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
         <v>26</v>
@@ -993,7 +1036,9 @@
         <v>7</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>60000</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
         <v>26</v>
@@ -1007,14 +1052,18 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>60000</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
         <v>26</v>
@@ -1033,7 +1082,9 @@
         <v>2</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>60000</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
         <v>26</v>
@@ -1052,7 +1103,9 @@
         <v>3</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>60000</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
         <v>26</v>
@@ -1071,7 +1124,9 @@
         <v>4</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>60000</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
         <v>26</v>
@@ -1090,7 +1145,9 @@
         <v>5</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>60000</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
         <v>26</v>
@@ -1109,7 +1166,9 @@
         <v>6</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>60000</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
         <v>26</v>
@@ -1128,7 +1187,9 @@
         <v>7</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>60000</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
         <v>26</v>
@@ -1143,7 +1204,9 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <v>60000</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
         <v>26</v>
@@ -1172,7 +1235,9 @@
         <v>1</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1">
+        <v>60000</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
         <v>26</v>
@@ -1191,7 +1256,9 @@
         <v>2</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <v>60000</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
         <v>26</v>
@@ -1210,7 +1277,9 @@
         <v>3</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <v>60000</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
         <v>26</v>
@@ -1229,7 +1298,9 @@
         <v>4</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1">
+        <v>60000</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
         <v>26</v>
@@ -1248,7 +1319,9 @@
         <v>5</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1">
+        <v>60000</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
         <v>26</v>
@@ -1267,7 +1340,9 @@
         <v>6</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1">
+        <v>60000</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
         <v>26</v>
@@ -1286,7 +1361,9 @@
         <v>7</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <v>60000</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
         <v>26</v>
@@ -1305,7 +1382,9 @@
         <v>8</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1">
+        <v>60000</v>
+      </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
         <v>26</v>
@@ -1322,7 +1401,9 @@
         <v>9</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1">
+        <v>60000</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
         <v>26</v>
@@ -1351,7 +1432,9 @@
         <v>1</v>
       </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1">
+        <v>60000</v>
+      </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1" t="s">
         <v>26</v>
@@ -1370,7 +1453,9 @@
         <v>2</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1">
+        <v>60000</v>
+      </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
         <v>26</v>
@@ -1389,7 +1474,9 @@
         <v>3</v>
       </c>
       <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1">
+        <v>60000</v>
+      </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
         <v>26</v>
@@ -1408,7 +1495,9 @@
         <v>4</v>
       </c>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1">
+        <v>60000</v>
+      </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
         <v>26</v>
@@ -1427,7 +1516,9 @@
         <v>5</v>
       </c>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1">
+        <v>60000</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
         <v>26</v>
@@ -1446,7 +1537,9 @@
         <v>6</v>
       </c>
       <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <v>60000</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
         <v>26</v>
@@ -1465,7 +1558,9 @@
         <v>7</v>
       </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1">
+        <v>60000</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
         <v>26</v>
@@ -1484,7 +1579,9 @@
         <v>8</v>
       </c>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <v>60000</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
         <v>26</v>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870F8BEA-70D8-4FC7-8F27-5EAFD62637F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5B8146-4ECD-4AA2-99CB-D6727BB9E394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="29">
   <si>
     <t>model</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>500008_1 500008_2 500008_3</t>
+  </si>
+  <si>
+    <t>description</t>
   </si>
 </sst>
 </file>
@@ -480,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50E1A44-280D-4411-9C01-14D3EB718FB5}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -488,10 +491,12 @@
     <col min="4" max="5" width="9.23046875" style="2"/>
     <col min="6" max="6" width="29.07421875" style="2" customWidth="1"/>
     <col min="7" max="8" width="11.69140625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.23046875" style="2"/>
+    <col min="9" max="11" width="9.23046875" style="2"/>
+    <col min="12" max="12" width="10.07421875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.23046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -525,8 +530,11 @@
       <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
@@ -556,8 +564,9 @@
       <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>100002</v>
       </c>
@@ -577,8 +586,9 @@
       <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>100003</v>
       </c>
@@ -598,8 +608,9 @@
       <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>100004</v>
       </c>
@@ -619,8 +630,9 @@
       <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>100005</v>
       </c>
@@ -640,8 +652,9 @@
       <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>100006</v>
       </c>
@@ -661,8 +674,9 @@
       <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>100007</v>
       </c>
@@ -682,8 +696,9 @@
       <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>100008</v>
       </c>
@@ -705,8 +720,9 @@
       <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>100009</v>
       </c>
@@ -726,8 +742,9 @@
       <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>100010</v>
       </c>
@@ -747,8 +764,9 @@
       <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>100011</v>
       </c>
@@ -768,8 +786,9 @@
       <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>100012</v>
       </c>
@@ -789,8 +808,9 @@
       <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>100013</v>
       </c>
@@ -810,8 +830,9 @@
       <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>100014</v>
       </c>
@@ -831,6 +852,7 @@
       <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="L15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -840,7 +862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC76538-67CE-4574-A08C-7F9575FC0AF6}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -849,10 +871,12 @@
     <col min="5" max="5" width="11.84375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.07421875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.69140625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.23046875" style="2"/>
+    <col min="8" max="11" width="9.23046875" style="2"/>
+    <col min="12" max="12" width="10.07421875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.23046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -886,8 +910,11 @@
       <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>500001</v>
       </c>
@@ -917,8 +944,9 @@
       <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>500002</v>
       </c>
@@ -938,8 +966,9 @@
       <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>500003</v>
       </c>
@@ -959,8 +988,9 @@
       <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>500004</v>
       </c>
@@ -980,8 +1010,9 @@
       <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>500005</v>
       </c>
@@ -1001,8 +1032,9 @@
       <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>500006</v>
       </c>
@@ -1022,8 +1054,9 @@
       <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>500007</v>
       </c>
@@ -1043,8 +1076,9 @@
       <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>500008</v>
       </c>
@@ -1068,8 +1102,9 @@
       <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>500009</v>
       </c>
@@ -1089,8 +1124,9 @@
       <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>500010</v>
       </c>
@@ -1110,8 +1146,9 @@
       <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>500011</v>
       </c>
@@ -1131,8 +1168,9 @@
       <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>500012</v>
       </c>
@@ -1152,8 +1190,9 @@
       <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>500013</v>
       </c>
@@ -1173,8 +1212,9 @@
       <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>500014</v>
       </c>
@@ -1194,8 +1234,9 @@
       <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1211,8 +1252,9 @@
       <c r="K16" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>500101</v>
       </c>
@@ -1242,8 +1284,9 @@
       <c r="K17" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>500102</v>
       </c>
@@ -1263,8 +1306,9 @@
       <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>500103</v>
       </c>
@@ -1284,8 +1328,9 @@
       <c r="K19" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>500104</v>
       </c>
@@ -1305,8 +1350,9 @@
       <c r="K20" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>500105</v>
       </c>
@@ -1326,8 +1372,9 @@
       <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>500106</v>
       </c>
@@ -1347,8 +1394,9 @@
       <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>500107</v>
       </c>
@@ -1368,8 +1416,9 @@
       <c r="K23" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>500108</v>
       </c>
@@ -1389,8 +1438,9 @@
       <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1408,8 +1458,9 @@
       <c r="K25" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>500201</v>
       </c>
@@ -1439,8 +1490,9 @@
       <c r="K26" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>500202</v>
       </c>
@@ -1460,8 +1512,9 @@
       <c r="K27" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>500203</v>
       </c>
@@ -1481,8 +1534,9 @@
       <c r="K28" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>500204</v>
       </c>
@@ -1502,8 +1556,9 @@
       <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>500205</v>
       </c>
@@ -1523,8 +1578,9 @@
       <c r="K30" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>500206</v>
       </c>
@@ -1544,8 +1600,9 @@
       <c r="K31" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>500207</v>
       </c>
@@ -1565,8 +1622,9 @@
       <c r="K32" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>500208</v>
       </c>
@@ -1586,6 +1644,7 @@
       <c r="K33" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="L33" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5B8146-4ECD-4AA2-99CB-D6727BB9E394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C1FD8B-D7C9-4240-85D9-68A6C35AE084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="30">
   <si>
     <t>model</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>description</t>
+  </si>
+  <si>
+    <t>in stock</t>
   </si>
 </sst>
 </file>
@@ -908,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>28</v>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C1FD8B-D7C9-4240-85D9-68A6C35AE084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AAB713-7A55-4BEB-BBA1-BF43A1DD9BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -531,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>28</v>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB91D6B-364F-4A91-A2D5-319288D0D585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC33E12D-70B6-47CD-A339-477372EEFD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Native" sheetId="11" r:id="rId7"/>
     <sheet name="Dickies" sheetId="13" r:id="rId8"/>
     <sheet name="Skechers" sheetId="14" r:id="rId9"/>
+    <sheet name="Asics" sheetId="16" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="130">
   <si>
     <t>model</t>
   </si>
@@ -358,6 +359,86 @@
     <t>Бастапқыда баскетбол алаңына арналғанымен, кейін көше стилінің символына айналған 80-жылдардағы аңыз қайта оралды — мінсіз әрленген бөлшектермен және классикалық команда түстерімен. Өзінің танымал баскетбол стилінің арқасында Nike Dunk Low 80-жылдардың винтаж рухын қайта алып келеді, ал жұмсақ төмен жағындағы жағасы кез келген жерде жайлылық сыйлайды.
 Созданная для баскетбольной площадки, но ставшая уличной легендой, икона 80-х возвращается с идеально отполированными деталями и классическими командными цветами. Благодаря фирменному баскетбольному дизайну Nike Dunk Low приносит винтажный дух 80-х обратно на улицы, а мягкий низкий ворот обеспечивает комфорт, куда бы ты ни отправился.</t>
   </si>
+  <si>
+    <t>Asics</t>
+  </si>
+  <si>
+    <t>JOLT 3 PS</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>130001_1 130001_2 130001_3 130001_4</t>
+  </si>
+  <si>
+    <t>K4.5</t>
+  </si>
+  <si>
+    <t>K5</t>
+  </si>
+  <si>
+    <t>K5.5</t>
+  </si>
+  <si>
+    <t>K6</t>
+  </si>
+  <si>
+    <t>K6.5</t>
+  </si>
+  <si>
+    <t>K7</t>
+  </si>
+  <si>
+    <t>K7.5</t>
+  </si>
+  <si>
+    <t>K8</t>
+  </si>
+  <si>
+    <t>K8.5</t>
+  </si>
+  <si>
+    <t>K9</t>
+  </si>
+  <si>
+    <t>K9.5</t>
+  </si>
+  <si>
+    <t>K10</t>
+  </si>
+  <si>
+    <t>K11</t>
+  </si>
+  <si>
+    <t>K12</t>
+  </si>
+  <si>
+    <t>K13</t>
+  </si>
+  <si>
+    <t>32.5</t>
+  </si>
+  <si>
+    <t>33.5</t>
+  </si>
+  <si>
+    <t>34.5</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>Удобные и практичные детские кроссовки, созданные для активного образа жизни. Модель вдохновлена беговой линейкой ASICS GT и отлично подходит как для спорта, так и для повседневной носки.
+Комфорт на каждый день
+Продуманная посадка в передней части стопы обеспечивает удобство даже при длительном ношении. Лёгкая конструкция снижает нагрузку на ноги ребёнка.
+Дышащие материалы
+Сетчатый верх способствует циркуляции воздуха и помогает сохранять комфортную температуру внутри обуви.
+Надёжная фиксация и поддержка
+Синтетические накладки усиливают конструкцию верха и обеспечивают дополнительную стабильность стопы.
+Износостойкость
+Усиленный носок и прочная резиновая подошва делают модель устойчивой к активному использованию и продлевают срок службы.</t>
+  </si>
 </sst>
 </file>
 
@@ -367,7 +448,7 @@
     <numFmt numFmtId="164" formatCode="0.0_ ;[Red]\-0.0\ "/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,13 +464,27 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00184F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -432,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -463,6 +558,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11637,6 +11735,896 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064B5749-20E2-4B7E-AD5C-A725C3BDEA3B}">
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="15.15234375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.23046875" style="2"/>
+    <col min="12" max="12" width="66.765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" spans="1:18" ht="291.45" x14ac:dyDescent="0.4">
+      <c r="A2" s="1">
+        <v>130001</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" s="12">
+        <v>19.5</v>
+      </c>
+      <c r="I2" s="5">
+        <f>M2</f>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="4">
+        <f>(N2*75+N2*75*0.01+12500+4200)/0.95</f>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N2" s="2">
+        <v>70</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A3" s="1">
+        <v>130002</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="12">
+        <v>20.5</v>
+      </c>
+      <c r="I3" s="5">
+        <f t="shared" ref="I3:I25" si="0">M3</f>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="4">
+        <f t="shared" ref="M3:M25" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N3" s="2">
+        <v>70</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>130003</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="12">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N4" s="2">
+        <v>70</v>
+      </c>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
+        <v>130004</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="12">
+        <v>21.5</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N5" s="2">
+        <v>70</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>130005</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="12">
+        <v>22.5</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N6" s="2">
+        <v>70</v>
+      </c>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>130006</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" s="12">
+        <v>23</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N7" s="2">
+        <v>70</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A8" s="1">
+        <v>130007</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="12">
+        <v>23.5</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N8" s="2">
+        <v>70</v>
+      </c>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A9" s="1">
+        <v>130008</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="12">
+        <v>24</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N9" s="2">
+        <v>70</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A10" s="1">
+        <v>130009</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H10" s="12">
+        <v>25</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N10" s="2">
+        <v>70</v>
+      </c>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A11" s="1">
+        <v>130010</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="12">
+        <v>25.5</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N11" s="2">
+        <v>70</v>
+      </c>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A12" s="1">
+        <v>130011</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="12">
+        <v>26</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N12" s="2">
+        <v>70</v>
+      </c>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A13" s="1">
+        <v>130012</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" s="12">
+        <v>26.5</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N13" s="2">
+        <v>70</v>
+      </c>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A14" s="1">
+        <v>130013</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="12">
+        <v>27</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N14" s="2">
+        <v>70</v>
+      </c>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A15" s="1">
+        <v>130014</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="12">
+        <v>28.5</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N15" s="2">
+        <v>70</v>
+      </c>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
+        <v>130015</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="12">
+        <v>30</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N16" s="2">
+        <v>70</v>
+      </c>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A17" s="1">
+        <v>130016</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="12">
+        <v>31.5</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N17" s="2">
+        <v>70</v>
+      </c>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A18" s="1">
+        <v>130017</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="12">
+        <v>1</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N18" s="2">
+        <v>70</v>
+      </c>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A19" s="1">
+        <v>130018</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="12">
+        <v>33</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N19" s="2">
+        <v>70</v>
+      </c>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A20" s="1">
+        <v>130019</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="12">
+        <v>2</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N20" s="2">
+        <v>70</v>
+      </c>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A21" s="1">
+        <v>130020</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N21" s="2">
+        <v>70</v>
+      </c>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A22" s="1">
+        <v>130021</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="12">
+        <v>3</v>
+      </c>
+      <c r="H22" s="12">
+        <v>35</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="4">
+        <f t="shared" si="1"/>
+        <v>23160.526315789473</v>
+      </c>
+      <c r="N22" s="2">
+        <v>70</v>
+      </c>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A23" s="1">
+        <v>130022</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A24" s="1">
+        <v>130023</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A25" s="1">
+        <v>130024</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A26" s="1">
+        <v>130025</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A27" s="1">
+        <v>130026</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC76538-67CE-4574-A08C-7F9575FC0AF6}">
   <dimension ref="A1:N33"/>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC33E12D-70B6-47CD-A339-477372EEFD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C683AF-325A-45C5-9E26-557F20A5C38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="134">
   <si>
     <t>model</t>
   </si>
@@ -439,6 +439,18 @@
 Износостойкость
 Усиленный носок и прочная резиновая подошва делают модель устойчивой к активному использованию и продлевают срок службы.</t>
   </si>
+  <si>
+    <t>Runfalcon 2.0 EL K</t>
+  </si>
+  <si>
+    <t>boys</t>
+  </si>
+  <si>
+    <t>10,5K</t>
+  </si>
+  <si>
+    <t>Кроссовки созданы для активного повседневного использования — школа, прогулки, спорт. Верх выполнен из дышащей сетки, которая обеспечивает вентиляцию и комфорт в течение дня. Модель отличается легкой конструкцией и хорошей амортизацией, благодаря EVA-пене в подошве, что снижает нагрузку на стопу при беге и ходьбе. Используются переработанные материалы (не менее 50%), что соответствует экологической стратегии adidas.</t>
+  </si>
 </sst>
 </file>
 
@@ -527,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -560,9 +572,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -11850,7 +11864,7 @@
         <v>20.5</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I25" si="0">M3</f>
+        <f t="shared" ref="I3:I22" si="0">M3</f>
         <v>23160.526315789473</v>
       </c>
       <c r="J3" s="1"/>
@@ -11859,7 +11873,7 @@
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="4">
-        <f t="shared" ref="M3:M25" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
+        <f t="shared" ref="M3:M22" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
         <v>23160.526315789473</v>
       </c>
       <c r="N3" s="2">
@@ -15226,6 +15240,7 @@
     <col min="3" max="3" width="42" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="60.53515625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9.23046875" style="2"/>
+    <col min="12" max="12" width="76.07421875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
@@ -15335,7 +15350,7 @@
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="4">
-        <f t="shared" ref="M3:M10" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
+        <f t="shared" ref="M3:M11" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
         <v>43812.368421052633</v>
       </c>
       <c r="N3" s="2">
@@ -15564,18 +15579,41 @@
         <v>900010</v>
       </c>
       <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="5"/>
+      <c r="C11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="1">
+        <v>900010</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" s="1">
+        <v>29</v>
+      </c>
+      <c r="I11" s="5">
+        <v>23000</v>
+      </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="2"/>
+      <c r="K11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="M11" s="4">
+        <f t="shared" si="1"/>
+        <v>22363.157894736843</v>
+      </c>
+      <c r="N11" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -15591,7 +15629,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="L12" s="14"/>
       <c r="M12" s="4"/>
       <c r="N12" s="2"/>
     </row>
@@ -15609,7 +15647,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="L13" s="14"/>
       <c r="M13" s="4"/>
       <c r="N13" s="2"/>
     </row>
@@ -15627,7 +15665,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="L14" s="14"/>
       <c r="M14" s="4"/>
       <c r="N14" s="2"/>
     </row>
@@ -15645,7 +15683,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="L15" s="14"/>
       <c r="M15" s="4"/>
       <c r="N15" s="2"/>
     </row>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C683AF-325A-45C5-9E26-557F20A5C38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F2AE0C-F5FA-4A3C-9A10-28A3628BB09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="135">
   <si>
     <t>model</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>Кроссовки созданы для активного повседневного использования — школа, прогулки, спорт. Верх выполнен из дышащей сетки, которая обеспечивает вентиляцию и комфорт в течение дня. Модель отличается легкой конструкцией и хорошей амортизацией, благодаря EVA-пене в подошве, что снижает нагрузку на стопу при беге и ходьбе. Используются переработанные материалы (не менее 50%), что соответствует экологической стратегии adidas.</t>
+  </si>
+  <si>
+    <t>900010_1 900010_2 900010_3 900010_4 900010_5 900010_6</t>
   </si>
 </sst>
 </file>
@@ -15588,8 +15591,8 @@
       <c r="E11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="1">
-        <v>900010</v>
+      <c r="F11" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>132</v>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F2AE0C-F5FA-4A3C-9A10-28A3628BB09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000A9D02-FF1D-48FC-B765-6C5261B45FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000A9D02-FF1D-48FC-B765-6C5261B45FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13582D7B-280A-4431-A326-6ED13554BFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="119">
   <si>
     <t>model</t>
   </si>
@@ -372,61 +372,7 @@
     <t>130001_1 130001_2 130001_3 130001_4</t>
   </si>
   <si>
-    <t>K4.5</t>
-  </si>
-  <si>
-    <t>K5</t>
-  </si>
-  <si>
-    <t>K5.5</t>
-  </si>
-  <si>
-    <t>K6</t>
-  </si>
-  <si>
-    <t>K6.5</t>
-  </si>
-  <si>
-    <t>K7</t>
-  </si>
-  <si>
-    <t>K7.5</t>
-  </si>
-  <si>
-    <t>K8</t>
-  </si>
-  <si>
-    <t>K8.5</t>
-  </si>
-  <si>
-    <t>K9</t>
-  </si>
-  <si>
-    <t>K9.5</t>
-  </si>
-  <si>
-    <t>K10</t>
-  </si>
-  <si>
-    <t>K11</t>
-  </si>
-  <si>
-    <t>K12</t>
-  </si>
-  <si>
     <t>K13</t>
-  </si>
-  <si>
-    <t>32.5</t>
-  </si>
-  <si>
-    <t>33.5</t>
-  </si>
-  <si>
-    <t>34.5</t>
-  </si>
-  <si>
-    <t>K4</t>
   </si>
   <si>
     <t>Удобные и практичные детские кроссовки, созданные для активного образа жизни. Модель вдохновлена беговой линейкой ASICS GT и отлично подходит как для спорта, так и для повседневной носки.
@@ -453,6 +399,12 @@
   </si>
   <si>
     <t>900010_1 900010_2 900010_3 900010_4 900010_5 900010_6</t>
+  </si>
+  <si>
+    <t>130002_1 130002_2 130002_3 130002_4</t>
+  </si>
+  <si>
+    <t>k12</t>
   </si>
 </sst>
 </file>
@@ -578,8 +530,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -11803,6 +11757,9 @@
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:18" ht="291.45" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
@@ -11824,10 +11781,10 @@
         <v>109</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H2" s="12">
-        <v>19.5</v>
+        <v>31.5</v>
       </c>
       <c r="I2" s="5">
         <f>M2</f>
@@ -11835,10 +11792,10 @@
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="M2" s="4">
         <f>(N2*75+N2*75*0.01+12500+4200)/0.95</f>
@@ -11847,44 +11804,54 @@
       <c r="N2" s="2">
         <v>70</v>
       </c>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+    </row>
+    <row r="3" spans="1:18" ht="291.45" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>130002</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="G3" s="12" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H3" s="12">
-        <v>20.5</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I22" si="0">M3</f>
+        <f>M3</f>
         <v>23160.526315789473</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="M3" s="4">
-        <f t="shared" ref="M3:M22" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
+        <f>(N3*75+N3*75*0.01+12500+4200)/0.95</f>
         <v>23160.526315789473</v>
       </c>
       <c r="N3" s="2">
         <v>70</v>
       </c>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
@@ -11895,31 +11862,17 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4" s="12">
-        <v>21</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N4" s="2">
-        <v>70</v>
-      </c>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="2"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
@@ -11930,31 +11883,17 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="12">
-        <v>21.5</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N5" s="2">
-        <v>70</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="2"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
@@ -11965,31 +11904,17 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="H6" s="12">
-        <v>22.5</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N6" s="2">
-        <v>70</v>
-      </c>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="2"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
@@ -12000,31 +11925,17 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="H7" s="12">
-        <v>23</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N7" s="2">
-        <v>70</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="2"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
@@ -12035,31 +11946,17 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="H8" s="12">
-        <v>23.5</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N8" s="2">
-        <v>70</v>
-      </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="2"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
@@ -12070,31 +11967,17 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="H9" s="12">
-        <v>24</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N9" s="2">
-        <v>70</v>
-      </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="2"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
@@ -12105,31 +11988,17 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="H10" s="12">
-        <v>25</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N10" s="2">
-        <v>70</v>
-      </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="2"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
@@ -12140,31 +12009,17 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="12">
-        <v>25.5</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N11" s="2">
-        <v>70</v>
-      </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="2"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -12175,31 +12030,17 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="H12" s="12">
-        <v>26</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N12" s="2">
-        <v>70</v>
-      </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="2"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
@@ -12210,31 +12051,17 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="12">
-        <v>26.5</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N13" s="2">
-        <v>70</v>
-      </c>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="2"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
@@ -12245,31 +12072,17 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="12">
-        <v>27</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N14" s="2">
-        <v>70</v>
-      </c>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="2"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
@@ -12280,31 +12093,17 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="12">
-        <v>28.5</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N15" s="2">
-        <v>70</v>
-      </c>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="2"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
@@ -12315,31 +12114,17 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="12">
-        <v>30</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N16" s="2">
-        <v>70</v>
-      </c>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="2"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
@@ -12350,31 +12135,17 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="12">
-        <v>31.5</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N17" s="2">
-        <v>70</v>
-      </c>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="2"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
@@ -12385,31 +12156,17 @@
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="12">
-        <v>1</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="6"/>
-      <c r="M18" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N18" s="2">
-        <v>70</v>
-      </c>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="2"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
@@ -12420,31 +12177,17 @@
       <c r="D19" s="6"/>
       <c r="E19" s="1"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="H19" s="12">
-        <v>33</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="6"/>
-      <c r="M19" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N19" s="2">
-        <v>70</v>
-      </c>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="2"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
@@ -12455,31 +12198,17 @@
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="12">
-        <v>2</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="6"/>
-      <c r="K20" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K20" s="1"/>
       <c r="L20" s="6"/>
-      <c r="M20" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N20" s="2">
-        <v>70</v>
-      </c>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="2"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
@@ -12490,31 +12219,17 @@
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="6"/>
-      <c r="K21" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K21" s="1"/>
       <c r="L21" s="6"/>
-      <c r="M21" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N21" s="2">
-        <v>70</v>
-      </c>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="2"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
@@ -12525,31 +12240,17 @@
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="12">
-        <v>3</v>
-      </c>
-      <c r="H22" s="12">
-        <v>35</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>23160.526315789473</v>
-      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="6"/>
-      <c r="K22" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="6"/>
-      <c r="M22" s="4">
-        <f t="shared" si="1"/>
-        <v>23160.526315789473</v>
-      </c>
-      <c r="N22" s="2">
-        <v>70</v>
-      </c>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="2"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
@@ -12568,6 +12269,9 @@
       <c r="L23" s="6"/>
       <c r="M23" s="4"/>
       <c r="N23" s="2"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
@@ -15583,19 +15287,19 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="H11" s="1">
         <v>29</v>
@@ -15607,8 +15311,8 @@
       <c r="K11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="13" t="s">
-        <v>133</v>
+      <c r="L11" t="s">
+        <v>115</v>
       </c>
       <c r="M11" s="4">
         <f t="shared" si="1"/>
@@ -15632,7 +15336,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="14"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="4"/>
       <c r="N12" s="2"/>
     </row>
@@ -15650,7 +15354,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="14"/>
+      <c r="L13" s="6"/>
       <c r="M13" s="4"/>
       <c r="N13" s="2"/>
     </row>
@@ -15668,7 +15372,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="14"/>
+      <c r="L14" s="6"/>
       <c r="M14" s="4"/>
       <c r="N14" s="2"/>
     </row>
@@ -15686,7 +15390,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="14"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="4"/>
       <c r="N15" s="2"/>
     </row>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13582D7B-280A-4431-A326-6ED13554BFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AA0301-D676-4827-9750-F33CA6CEF077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="123">
   <si>
     <t>model</t>
   </si>
@@ -405,6 +405,18 @@
   </si>
   <si>
     <t>k12</t>
+  </si>
+  <si>
+    <t>Court Borough Low 2</t>
+  </si>
+  <si>
+    <t>100335_1 100335_2 100335_3 100335_4 100335_5 100335_6</t>
+  </si>
+  <si>
+    <t>5y</t>
+  </si>
+  <si>
+    <t>Кроссовки Nike Court Borough Low 2 (GS) выполнены в классическом баскетбольном ретро-стиле, адаптированном для повседневного ношения. Верх сочетает натуральную и синтетическую кожу, обеспечивая прочность и поддержку. Модель отличается низким профилем, плотной фиксацией стопы за счёт шнуровки (иногда с липучкой в детских версиях) и перфорацией для вентиляции. Резиновая подошва с протектором обеспечивает сцепление и долговечность, а гибкие желобки улучшают естественное движение стопы.</t>
   </si>
 </sst>
 </file>
@@ -838,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50E1A44-280D-4411-9C01-14D3EB718FB5}">
-  <dimension ref="A1:N335"/>
+  <dimension ref="A1:N363"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -10123,7 +10135,7 @@
       </c>
       <c r="L287" s="1"/>
       <c r="M287" s="4">
-        <f t="shared" ref="M287:M335" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
+        <f t="shared" ref="M287:M336" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
         <v>74033.421052631587</v>
       </c>
       <c r="N287" s="2">
@@ -10274,7 +10286,7 @@
         <v>44</v>
       </c>
       <c r="I292" s="5">
-        <f t="shared" ref="I292:I335" si="14">M292</f>
+        <f t="shared" ref="I292:I336" si="14">M292</f>
         <v>74830.789473684214</v>
       </c>
       <c r="J292" s="1"/>
@@ -11698,6 +11710,183 @@
       </c>
       <c r="N335" s="2">
         <v>619</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A336" s="1">
+        <v>100335</v>
+      </c>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G336" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H336" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="I336" s="1">
+        <f t="shared" si="14"/>
+        <v>50112.368421052633</v>
+      </c>
+      <c r="J336" s="1"/>
+      <c r="K336" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L336" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M336" s="2">
+        <f t="shared" si="13"/>
+        <v>50112.368421052633</v>
+      </c>
+      <c r="N336" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A337" s="1">
+        <v>100336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A338" s="1">
+        <v>100337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A339" s="1">
+        <v>100338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A340" s="1">
+        <v>100339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A341" s="1">
+        <v>100340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A342" s="1">
+        <v>100341</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A343" s="1">
+        <v>100342</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A344" s="1">
+        <v>100343</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A345" s="1">
+        <v>100344</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A346" s="1">
+        <v>100345</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A347" s="1">
+        <v>100346</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A348" s="1">
+        <v>100347</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A349" s="1">
+        <v>100348</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A350" s="1">
+        <v>100349</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A351" s="1">
+        <v>100350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A352" s="1">
+        <v>100351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A353" s="1">
+        <v>100352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A354" s="1">
+        <v>100353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A355" s="1">
+        <v>100354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A356" s="1">
+        <v>100355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A357" s="1">
+        <v>100356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A358" s="1">
+        <v>100357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A359" s="1">
+        <v>100358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A360" s="1">
+        <v>100359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A361" s="1">
+        <v>100360</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A362" s="1">
+        <v>100361</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A363" s="1">
+        <v>100362</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AA0301-D676-4827-9750-F33CA6CEF077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52181513-F941-4397-AD2C-8409771F6C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="123">
   <si>
     <t>model</t>
   </si>
@@ -413,10 +413,10 @@
     <t>100335_1 100335_2 100335_3 100335_4 100335_5 100335_6</t>
   </si>
   <si>
-    <t>5y</t>
+    <t>Кроссовки Nike Court Borough Low 2 (GS) выполнены в классическом баскетбольном ретро-стиле, адаптированном для повседневного ношения. Верх сочетает натуральную и синтетическую кожу, обеспечивая прочность и поддержку. Модель отличается низким профилем, плотной фиксацией стопы за счёт шнуровки (иногда с липучкой в детских версиях) и перфорацией для вентиляции. Резиновая подошва с протектором обеспечивает сцепление и долговечность, а гибкие желобки улучшают естественное движение стопы.</t>
   </si>
   <si>
-    <t>Кроссовки Nike Court Borough Low 2 (GS) выполнены в классическом баскетбольном ретро-стиле, адаптированном для повседневного ношения. Верх сочетает натуральную и синтетическую кожу, обеспечивая прочность и поддержку. Модель отличается низким профилем, плотной фиксацией стопы за счёт шнуровки (иногда с липучкой в детских версиях) и перфорацией для вентиляции. Резиновая подошва с протектором обеспечивает сцепление и долговечность, а гибкие желобки улучшают естественное движение стопы.</t>
+    <t>100336_1 100336_2 100336_3</t>
   </si>
 </sst>
 </file>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="L287" s="1"/>
       <c r="M287" s="4">
-        <f t="shared" ref="M287:M336" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
+        <f t="shared" ref="M287:M338" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
         <v>74033.421052631587</v>
       </c>
       <c r="N287" s="2">
@@ -10286,7 +10286,7 @@
         <v>44</v>
       </c>
       <c r="I292" s="5">
-        <f t="shared" ref="I292:I336" si="14">M292</f>
+        <f t="shared" ref="I292:I338" si="14">M292</f>
         <v>74830.789473684214</v>
       </c>
       <c r="J292" s="1"/>
@@ -11729,9 +11729,7 @@
       <c r="F336" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G336" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="G336" s="1"/>
       <c r="H336" s="1">
         <v>37.5</v>
       </c>
@@ -11744,7 +11742,7 @@
         <v>25</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M336" s="2">
         <f t="shared" si="13"/>
@@ -11754,82 +11752,128 @@
         <v>309</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A337" s="1">
         <v>100336</v>
       </c>
-    </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="D337" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F337" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H337" s="2">
+        <v>36</v>
+      </c>
+      <c r="I337" s="2">
+        <f t="shared" si="14"/>
+        <v>53301.84210526316</v>
+      </c>
+      <c r="K337" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L337" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M337" s="2">
+        <f t="shared" si="13"/>
+        <v>53301.84210526316</v>
+      </c>
+      <c r="N337" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A338" s="1">
         <v>100337</v>
       </c>
-    </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="H338" s="2">
+        <v>40</v>
+      </c>
+      <c r="I338" s="2">
+        <f t="shared" si="14"/>
+        <v>53301.84210526316</v>
+      </c>
+      <c r="K338" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M338" s="2">
+        <f t="shared" si="13"/>
+        <v>53301.84210526316</v>
+      </c>
+      <c r="N338" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A339" s="1">
         <v>100338</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A340" s="1">
         <v>100339</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
         <v>100340</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
         <v>100341</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A343" s="1">
         <v>100342</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A344" s="1">
         <v>100343</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A345" s="1">
         <v>100344</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
         <v>100345</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
         <v>100346</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
         <v>100347</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
         <v>100348</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
         <v>100349</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
         <v>100350</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A352" s="1">
         <v>100351</v>
       </c>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52181513-F941-4397-AD2C-8409771F6C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28009184-94FB-4311-B4A0-FC0EECD1DDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28009184-94FB-4311-B4A0-FC0EECD1DDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EDBEC4-0FBF-4B8E-8C36-5172BDCAF0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="126">
   <si>
     <t>model</t>
   </si>
@@ -418,6 +418,17 @@
   <si>
     <t>100336_1 100336_2 100336_3</t>
   </si>
+  <si>
+    <t>Revolution 6 NN</t>
+  </si>
+  <si>
+    <t>100338_1 100338_2 100338_3 100338_4 100338_5 100338_6</t>
+  </si>
+  <si>
+    <t>Эта модель выделяется уникальным дизайном и превосходными характеристиками. Верхняя часть выполнена из сетчатого материала, обеспечивающего отличную воздухопроницаемость, что позволяет ногам оставаться сухими и комфортными даже во время длительных тренировок. Сетчатый материал также обладает хорошими амортизирующими свойствами, эффективно снижая ударную нагрузку при беге и обеспечивая стабильную поддержку стопы.
+Кроме того, кроссовки отличаются противоскользящими и износостойкими свойствами. Подошва изготовлена из специальной резиновой смеси, обеспечивающей превосходное сцепление с поверхностью и долговечность. Благодаря этому обувь гарантирует устойчивость как на ровной дороге, так и на сложном рельефе. Резиновая подошва также обладает хорошей упругостью, создавая комфортную амортизацию и снижая усталость ног.
+В дизайне Nike REVOLUTION 6 Next Nature Low NN использована классическая черно-белая цветовая гамма, сочетающая минимализм и современность. Низкий силуэт не только подчеркивает линии стопы, но и обеспечивает повышенную гибкость и свободу движений во время активности.</t>
+  </si>
 </sst>
 </file>
 
@@ -542,10 +553,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -850,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50E1A44-280D-4411-9C01-14D3EB718FB5}">
-  <dimension ref="A1:N363"/>
+  <dimension ref="A1:O363"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -10135,7 +10148,7 @@
       </c>
       <c r="L287" s="1"/>
       <c r="M287" s="4">
-        <f t="shared" ref="M287:M338" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
+        <f t="shared" ref="M287:M339" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
         <v>74033.421052631587</v>
       </c>
       <c r="N287" s="2">
@@ -10286,7 +10299,7 @@
         <v>44</v>
       </c>
       <c r="I292" s="5">
-        <f t="shared" ref="I292:I338" si="14">M292</f>
+        <f t="shared" ref="I292:I339" si="14">M292</f>
         <v>74830.789473684214</v>
       </c>
       <c r="J292" s="1"/>
@@ -11224,7 +11237,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A321" s="1">
         <v>100320</v>
       </c>
@@ -11256,7 +11269,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A322" s="1">
         <v>100321</v>
       </c>
@@ -11288,7 +11301,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A323" s="1">
         <v>100322</v>
       </c>
@@ -11320,7 +11333,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A324" s="1">
         <v>100323</v>
       </c>
@@ -11352,7 +11365,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A325" s="1">
         <v>100324</v>
       </c>
@@ -11384,7 +11397,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="326" spans="1:14" ht="247.75" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:15" ht="247.75" x14ac:dyDescent="0.4">
       <c r="A326" s="1">
         <v>100325</v>
       </c>
@@ -11424,7 +11437,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A327" s="1">
         <v>100326</v>
       </c>
@@ -11456,7 +11469,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A328" s="1">
         <v>100327</v>
       </c>
@@ -11488,7 +11501,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A329" s="1">
         <v>100328</v>
       </c>
@@ -11520,7 +11533,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A330" s="1">
         <v>100329</v>
       </c>
@@ -11552,7 +11565,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A331" s="1">
         <v>100330</v>
       </c>
@@ -11584,7 +11597,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A332" s="1">
         <v>100331</v>
       </c>
@@ -11616,7 +11629,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A333" s="1">
         <v>100332</v>
       </c>
@@ -11648,7 +11661,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A334" s="1">
         <v>100333</v>
       </c>
@@ -11680,7 +11693,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A335" s="1">
         <v>100334</v>
       </c>
@@ -11712,7 +11725,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A336" s="1">
         <v>100335</v>
       </c>
@@ -11726,9 +11739,7 @@
       <c r="E336" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F336" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="F336" s="1"/>
       <c r="G336" s="1"/>
       <c r="H336" s="1">
         <v>37.5</v>
@@ -11751,31 +11762,36 @@
       <c r="N336" s="2">
         <v>309</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O336" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A337" s="1">
         <v>100336</v>
       </c>
-      <c r="D337" s="2" t="s">
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E337" s="2" t="s">
+      <c r="E337" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F337" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H337" s="2">
+      <c r="F337" s="1"/>
+      <c r="G337" s="1"/>
+      <c r="H337" s="1">
         <v>36</v>
       </c>
-      <c r="I337" s="2">
+      <c r="I337" s="1">
         <f t="shared" si="14"/>
         <v>53301.84210526316</v>
       </c>
+      <c r="J337" s="1"/>
       <c r="K337" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L337" s="2" t="s">
+      <c r="L337" s="1" t="s">
         <v>121</v>
       </c>
       <c r="M337" s="2">
@@ -11785,21 +11801,32 @@
       <c r="N337" s="2">
         <v>349</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O337" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A338" s="1">
         <v>100337</v>
       </c>
-      <c r="H338" s="2">
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1">
         <v>40</v>
       </c>
-      <c r="I338" s="2">
+      <c r="I338" s="1">
         <f t="shared" si="14"/>
         <v>53301.84210526316</v>
       </c>
+      <c r="J338" s="1"/>
       <c r="K338" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="L338" s="1"/>
       <c r="M338" s="2">
         <f t="shared" si="13"/>
         <v>53301.84210526316</v>
@@ -11808,72 +11835,104 @@
         <v>349</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:15" ht="378.9" x14ac:dyDescent="0.4">
       <c r="A339" s="1">
         <v>100338</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C339" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F339" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H339" s="2">
+        <v>41</v>
+      </c>
+      <c r="I339" s="2">
+        <f t="shared" si="14"/>
+        <v>48118.947368421053</v>
+      </c>
+      <c r="K339" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L339" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="M339" s="2">
+        <f t="shared" si="13"/>
+        <v>48118.947368421053</v>
+      </c>
+      <c r="N339" s="2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A340" s="1">
         <v>100339</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
         <v>100340</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
         <v>100341</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A343" s="1">
         <v>100342</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A344" s="1">
         <v>100343</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A345" s="1">
         <v>100344</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
         <v>100345</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
         <v>100346</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
         <v>100347</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
         <v>100348</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
         <v>100349</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
         <v>100350</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A352" s="1">
         <v>100351</v>
       </c>
@@ -11990,9 +12049,6 @@
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:18" ht="291.45" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
@@ -12502,9 +12558,6 @@
       <c r="L23" s="6"/>
       <c r="M23" s="4"/>
       <c r="N23" s="2"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="1">

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EDBEC4-0FBF-4B8E-8C36-5172BDCAF0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16445551-FCD7-45CE-AF74-3232399F64C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="124">
   <si>
     <t>model</t>
   </si>
@@ -413,9 +413,6 @@
     <t>100335_1 100335_2 100335_3 100335_4 100335_5 100335_6</t>
   </si>
   <si>
-    <t>Кроссовки Nike Court Borough Low 2 (GS) выполнены в классическом баскетбольном ретро-стиле, адаптированном для повседневного ношения. Верх сочетает натуральную и синтетическую кожу, обеспечивая прочность и поддержку. Модель отличается низким профилем, плотной фиксацией стопы за счёт шнуровки (иногда с липучкой в детских версиях) и перфорацией для вентиляции. Резиновая подошва с протектором обеспечивает сцепление и долговечность, а гибкие желобки улучшают естественное движение стопы.</t>
-  </si>
-  <si>
     <t>100336_1 100336_2 100336_3</t>
   </si>
   <si>
@@ -423,11 +420,6 @@
   </si>
   <si>
     <t>100338_1 100338_2 100338_3 100338_4 100338_5 100338_6</t>
-  </si>
-  <si>
-    <t>Эта модель выделяется уникальным дизайном и превосходными характеристиками. Верхняя часть выполнена из сетчатого материала, обеспечивающего отличную воздухопроницаемость, что позволяет ногам оставаться сухими и комфортными даже во время длительных тренировок. Сетчатый материал также обладает хорошими амортизирующими свойствами, эффективно снижая ударную нагрузку при беге и обеспечивая стабильную поддержку стопы.
-Кроме того, кроссовки отличаются противоскользящими и износостойкими свойствами. Подошва изготовлена из специальной резиновой смеси, обеспечивающей превосходное сцепление с поверхностью и долговечность. Благодаря этому обувь гарантирует устойчивость как на ровной дороге, так и на сложном рельефе. Резиновая подошва также обладает хорошей упругостью, создавая комфортную амортизацию и снижая усталость ног.
-В дизайне Nike REVOLUTION 6 Next Nature Low NN использована классическая черно-белая цветовая гамма, сочетающая минимализм и современность. Низкий силуэт не только подчеркивает линии стопы, но и обеспечивает повышенную гибкость и свободу движений во время активности.</t>
   </si>
 </sst>
 </file>
@@ -11752,9 +11744,7 @@
       <c r="K336" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L336" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="L336" s="1"/>
       <c r="M336" s="2">
         <f t="shared" si="13"/>
         <v>50112.368421052633</v>
@@ -11791,9 +11781,7 @@
       <c r="K337" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L337" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="L337" s="1"/>
       <c r="M337" s="2">
         <f t="shared" si="13"/>
         <v>53301.84210526316</v>
@@ -11802,7 +11790,7 @@
         <v>349</v>
       </c>
       <c r="O337" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="338" spans="1:15" x14ac:dyDescent="0.4">
@@ -11835,12 +11823,12 @@
         <v>349</v>
       </c>
     </row>
-    <row r="339" spans="1:15" ht="378.9" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A339" s="1">
         <v>100338</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>38</v>
@@ -11849,7 +11837,7 @@
         <v>43</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H339" s="2">
         <v>41</v>
@@ -11861,9 +11849,7 @@
       <c r="K339" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L339" s="14" t="s">
-        <v>125</v>
-      </c>
+      <c r="L339" s="14"/>
       <c r="M339" s="2">
         <f t="shared" si="13"/>
         <v>48118.947368421053</v>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16445551-FCD7-45CE-AF74-3232399F64C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21CF2BE-F986-4B06-918A-91F1A20BA22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="126">
   <si>
     <t>model</t>
   </si>
@@ -413,6 +413,9 @@
     <t>100335_1 100335_2 100335_3 100335_4 100335_5 100335_6</t>
   </si>
   <si>
+    <t>Кроссовки Nike Court Borough Low 2 (GS) выполнены в классическом баскетбольном ретро-стиле, адаптированном для повседневного ношения. Верх сочетает натуральную и синтетическую кожу, обеспечивая прочность и поддержку. Модель отличается низким профилем, плотной фиксацией стопы за счёт шнуровки (иногда с липучкой в детских версиях) и перфорацией для вентиляции. Резиновая подошва с протектором обеспечивает сцепление и долговечность, а гибкие желобки улучшают естественное движение стопы.</t>
+  </si>
+  <si>
     <t>100336_1 100336_2 100336_3</t>
   </si>
   <si>
@@ -420,6 +423,11 @@
   </si>
   <si>
     <t>100338_1 100338_2 100338_3 100338_4 100338_5 100338_6</t>
+  </si>
+  <si>
+    <t>Эта модель выделяется уникальным дизайном и превосходными характеристиками. Верхняя часть выполнена из сетчатого материала, обеспечивающего отличную воздухопроницаемость, что позволяет ногам оставаться сухими и комфортными даже во время длительных тренировок. Сетчатый материал также обладает хорошими амортизирующими свойствами, эффективно снижая ударную нагрузку при беге и обеспечивая стабильную поддержку стопы.
+Кроме того, кроссовки отличаются противоскользящими и износостойкими свойствами. Подошва изготовлена из специальной резиновой смеси, обеспечивающей превосходное сцепление с поверхностью и долговечность. Благодаря этому обувь гарантирует устойчивость как на ровной дороге, так и на сложном рельефе. Резиновая подошва также обладает хорошей упругостью, создавая комфортную амортизацию и снижая усталость ног.
+В дизайне Nike REVOLUTION 6 Next Nature Low NN использована классическая черно-белая цветовая гамма, сочетающая минимализм и современность. Низкий силуэт не только подчеркивает линии стопы, но и обеспечивает повышенную гибкость и свободу движений во время активности.</t>
   </si>
 </sst>
 </file>
@@ -469,7 +477,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -503,6 +511,19 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -548,8 +569,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -855,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50E1A44-280D-4411-9C01-14D3EB718FB5}">
-  <dimension ref="A1:O363"/>
+  <dimension ref="A1:N363"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -11229,7 +11250,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A321" s="1">
         <v>100320</v>
       </c>
@@ -11261,7 +11282,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A322" s="1">
         <v>100321</v>
       </c>
@@ -11293,7 +11314,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A323" s="1">
         <v>100322</v>
       </c>
@@ -11325,7 +11346,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A324" s="1">
         <v>100323</v>
       </c>
@@ -11357,7 +11378,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A325" s="1">
         <v>100324</v>
       </c>
@@ -11389,7 +11410,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="326" spans="1:15" ht="247.75" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:14" ht="247.75" x14ac:dyDescent="0.4">
       <c r="A326" s="1">
         <v>100325</v>
       </c>
@@ -11429,7 +11450,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A327" s="1">
         <v>100326</v>
       </c>
@@ -11461,7 +11482,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A328" s="1">
         <v>100327</v>
       </c>
@@ -11493,7 +11514,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A329" s="1">
         <v>100328</v>
       </c>
@@ -11525,7 +11546,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A330" s="1">
         <v>100329</v>
       </c>
@@ -11557,7 +11578,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A331" s="1">
         <v>100330</v>
       </c>
@@ -11589,7 +11610,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A332" s="1">
         <v>100331</v>
       </c>
@@ -11621,7 +11642,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A333" s="1">
         <v>100332</v>
       </c>
@@ -11653,7 +11674,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A334" s="1">
         <v>100333</v>
       </c>
@@ -11685,7 +11706,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A335" s="1">
         <v>100334</v>
       </c>
@@ -11717,7 +11738,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A336" s="1">
         <v>100335</v>
       </c>
@@ -11731,8 +11752,12 @@
       <c r="E336" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F336" s="1"/>
-      <c r="G336" s="1"/>
+      <c r="F336" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G336" s="1">
+        <v>6</v>
+      </c>
       <c r="H336" s="1">
         <v>37.5</v>
       </c>
@@ -11744,7 +11769,9 @@
       <c r="K336" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L336" s="1"/>
+      <c r="L336" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="M336" s="2">
         <f t="shared" si="13"/>
         <v>50112.368421052633</v>
@@ -11752,11 +11779,8 @@
       <c r="N336" s="2">
         <v>309</v>
       </c>
-      <c r="O336" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A337" s="1">
         <v>100336</v>
       </c>
@@ -11768,8 +11792,12 @@
       <c r="E337" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F337" s="1"/>
-      <c r="G337" s="1"/>
+      <c r="F337" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G337" s="1">
+        <v>6</v>
+      </c>
       <c r="H337" s="1">
         <v>36</v>
       </c>
@@ -11781,7 +11809,9 @@
       <c r="K337" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L337" s="1"/>
+      <c r="L337" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="M337" s="2">
         <f t="shared" si="13"/>
         <v>53301.84210526316</v>
@@ -11789,11 +11819,8 @@
       <c r="N337" s="2">
         <v>349</v>
       </c>
-      <c r="O337" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A338" s="1">
         <v>100337</v>
       </c>
@@ -11802,7 +11829,9 @@
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
-      <c r="G338" s="1"/>
+      <c r="G338" s="1">
+        <v>6</v>
+      </c>
       <c r="H338" s="1">
         <v>40</v>
       </c>
@@ -11823,33 +11852,40 @@
         <v>349</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:14" ht="378.9" x14ac:dyDescent="0.4">
       <c r="A339" s="1">
         <v>100338</v>
       </c>
-      <c r="C339" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D339" s="2" t="s">
+      <c r="B339" s="1"/>
+      <c r="C339" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E339" s="2" t="s">
+      <c r="E339" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F339" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H339" s="2">
+      <c r="F339" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G339" s="1">
+        <v>6</v>
+      </c>
+      <c r="H339" s="1">
         <v>41</v>
       </c>
-      <c r="I339" s="2">
+      <c r="I339" s="1">
         <f t="shared" si="14"/>
         <v>48118.947368421053</v>
       </c>
-      <c r="K339" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L339" s="14"/>
+      <c r="J339" s="1"/>
+      <c r="K339" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L339" s="9" t="s">
+        <v>125</v>
+      </c>
       <c r="M339" s="2">
         <f t="shared" si="13"/>
         <v>48118.947368421053</v>
@@ -11858,67 +11894,67 @@
         <v>284</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A340" s="1">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A340" s="14">
         <v>100339</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
         <v>100340</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
         <v>100341</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A343" s="1">
         <v>100342</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A344" s="1">
         <v>100343</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A345" s="1">
         <v>100344</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
         <v>100345</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
         <v>100346</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
         <v>100347</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
         <v>100348</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
         <v>100349</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
         <v>100350</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A352" s="1">
         <v>100351</v>
       </c>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21CF2BE-F986-4B06-918A-91F1A20BA22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C48CFFE-1365-4577-AA5C-11F4308E3B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="129">
   <si>
     <t>model</t>
   </si>
@@ -428,6 +428,15 @@
     <t>Эта модель выделяется уникальным дизайном и превосходными характеристиками. Верхняя часть выполнена из сетчатого материала, обеспечивающего отличную воздухопроницаемость, что позволяет ногам оставаться сухими и комфортными даже во время длительных тренировок. Сетчатый материал также обладает хорошими амортизирующими свойствами, эффективно снижая ударную нагрузку при беге и обеспечивая стабильную поддержку стопы.
 Кроме того, кроссовки отличаются противоскользящими и износостойкими свойствами. Подошва изготовлена из специальной резиновой смеси, обеспечивающей превосходное сцепление с поверхностью и долговечность. Благодаря этому обувь гарантирует устойчивость как на ровной дороге, так и на сложном рельефе. Резиновая подошва также обладает хорошей упругостью, создавая комфортную амортизацию и снижая усталость ног.
 В дизайне Nike REVOLUTION 6 Next Nature Low NN использована классическая черно-белая цветовая гамма, сочетающая минимализм и современность. Низкий силуэт не только подчеркивает линии стопы, но и обеспечивает повышенную гибкость и свободу движений во время активности.</t>
+  </si>
+  <si>
+    <t>5y</t>
+  </si>
+  <si>
+    <t>4y</t>
+  </si>
+  <si>
+    <t>7y</t>
   </si>
 </sst>
 </file>
@@ -11755,8 +11764,8 @@
       <c r="F336" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G336" s="1">
-        <v>6</v>
+      <c r="G336" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="H336" s="1">
         <v>37.5</v>
@@ -11795,8 +11804,8 @@
       <c r="F337" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G337" s="1">
-        <v>6</v>
+      <c r="G337" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H337" s="1">
         <v>36</v>
@@ -11829,8 +11838,8 @@
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
-      <c r="G338" s="1">
-        <v>6</v>
+      <c r="G338" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="H338" s="1">
         <v>40</v>
@@ -11870,7 +11879,7 @@
         <v>124</v>
       </c>
       <c r="G339" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H339" s="1">
         <v>41</v>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C48CFFE-1365-4577-AA5C-11F4308E3B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695EDDD4-F558-44E9-A2C3-D7A2A1931FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="134">
   <si>
     <t>model</t>
   </si>
@@ -438,6 +438,41 @@
   <si>
     <t>7y</t>
   </si>
+  <si>
+    <t>https://ibb.co.com/qMZNjg2v
+https://ibb.co.com/8nXXptJh 
+https://ibb.co.com/xSf1R34J 
+https://ibb.co.com/bjVzWtHV 
+https://ibb.co.com/Zz2ZFSs6 
+https://ibb.co.com/RGGtkY9L</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/HL9sCCvq
+https://ibb.co.com/pvFkhMQK
+https://ibb.co.com/sp1k7mt7
+https://ibb.co.com/M5fPNLgd</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/pBnKmYp3
+https://ibb.co.com/DP4Q2qhw
+https://ibb.co.com/tw2qGfKD</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/kVnjLhST
+https://ibb.co.com/jZrG5VD4
+https://ibb.co.com/fVfk5tbk
+https://ibb.co.com/840Khwpy
+https://ibb.co.com/gM01nrbj
+https://ibb.co.com/ZpCL07Z2</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/Qvxk9yf0
+https://ibb.co.com/ZpNh8TLk
+https://ibb.co.com/pBz6GC1J
+https://ibb.co.com/svyYfZ5w
+https://ibb.co.com/zTrKmB47
+https://ibb.co.com/gMdqw04Q</t>
+  </si>
 </sst>
 </file>
 
@@ -447,7 +482,7 @@
     <numFmt numFmtId="164" formatCode="0.0_ ;[Red]\-0.0\ "/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +501,15 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00184F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -536,10 +580,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -578,11 +623,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -885,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50E1A44-280D-4411-9C01-14D3EB718FB5}">
-  <dimension ref="A1:N363"/>
+  <dimension ref="A1:O363"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="9.23046875" style="2"/>
@@ -899,7 +955,9 @@
     <col min="10" max="10" width="8.15234375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.15234375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="48.84375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.23046875" style="2"/>
+    <col min="13" max="14" width="9.23046875" style="2"/>
+    <col min="15" max="15" width="27.3046875" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.23046875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18.45" customHeight="1" x14ac:dyDescent="0.4">
@@ -11259,7 +11317,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A321" s="1">
         <v>100320</v>
       </c>
@@ -11291,7 +11349,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A322" s="1">
         <v>100321</v>
       </c>
@@ -11323,7 +11381,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A323" s="1">
         <v>100322</v>
       </c>
@@ -11355,7 +11413,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A324" s="1">
         <v>100323</v>
       </c>
@@ -11387,7 +11445,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A325" s="1">
         <v>100324</v>
       </c>
@@ -11419,7 +11477,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="326" spans="1:14" ht="247.75" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:15" ht="247.75" x14ac:dyDescent="0.4">
       <c r="A326" s="1">
         <v>100325</v>
       </c>
@@ -11459,7 +11517,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A327" s="1">
         <v>100326</v>
       </c>
@@ -11491,7 +11549,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A328" s="1">
         <v>100327</v>
       </c>
@@ -11523,7 +11581,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A329" s="1">
         <v>100328</v>
       </c>
@@ -11555,7 +11613,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A330" s="1">
         <v>100329</v>
       </c>
@@ -11587,7 +11645,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A331" s="1">
         <v>100330</v>
       </c>
@@ -11619,7 +11677,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A332" s="1">
         <v>100331</v>
       </c>
@@ -11651,7 +11709,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A333" s="1">
         <v>100332</v>
       </c>
@@ -11683,7 +11741,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A334" s="1">
         <v>100333</v>
       </c>
@@ -11715,7 +11773,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A335" s="1">
         <v>100334</v>
       </c>
@@ -11747,7 +11805,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="336" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:15" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A336" s="1">
         <v>100335</v>
       </c>
@@ -11788,8 +11846,11 @@
       <c r="N336" s="2">
         <v>309</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O336" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15" ht="102" x14ac:dyDescent="0.4">
       <c r="A337" s="1">
         <v>100336</v>
       </c>
@@ -11828,8 +11889,11 @@
       <c r="N337" s="2">
         <v>349</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O337" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A338" s="1">
         <v>100337</v>
       </c>
@@ -11861,7 +11925,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="339" spans="1:14" ht="378.9" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:15" ht="378.9" x14ac:dyDescent="0.4">
       <c r="A339" s="1">
         <v>100338</v>
       </c>
@@ -11902,68 +11966,71 @@
       <c r="N339" s="2">
         <v>284</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A340" s="14">
+      <c r="O339" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A340" s="15">
         <v>100339</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
         <v>100340</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
         <v>100341</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A343" s="1">
         <v>100342</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A344" s="1">
         <v>100343</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A345" s="1">
         <v>100344</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
         <v>100345</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
         <v>100346</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
         <v>100347</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
         <v>100348</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
         <v>100349</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
         <v>100350</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A352" s="1">
         <v>100351</v>
       </c>
@@ -12039,6 +12106,7 @@
     <col min="6" max="6" width="60.53515625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9.23046875" style="2"/>
     <col min="12" max="12" width="66.765625" customWidth="1"/>
+    <col min="15" max="15" width="26.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.4">
@@ -12124,6 +12192,9 @@
       <c r="N2" s="2">
         <v>70</v>
       </c>
+      <c r="O2" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
@@ -12169,9 +12240,12 @@
       <c r="N3" s="2">
         <v>70</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
+      <c r="O3" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
@@ -12190,9 +12264,10 @@
       <c r="L4" s="1"/>
       <c r="M4" s="4"/>
       <c r="N4" s="2"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
@@ -12211,9 +12286,10 @@
       <c r="L5" s="1"/>
       <c r="M5" s="4"/>
       <c r="N5" s="2"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
@@ -12232,9 +12308,10 @@
       <c r="L6" s="1"/>
       <c r="M6" s="4"/>
       <c r="N6" s="2"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
@@ -12253,9 +12330,10 @@
       <c r="L7" s="1"/>
       <c r="M7" s="4"/>
       <c r="N7" s="2"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
@@ -12274,9 +12352,10 @@
       <c r="L8" s="1"/>
       <c r="M8" s="4"/>
       <c r="N8" s="2"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
@@ -12295,9 +12374,10 @@
       <c r="L9" s="1"/>
       <c r="M9" s="4"/>
       <c r="N9" s="2"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
@@ -12316,9 +12396,10 @@
       <c r="L10" s="1"/>
       <c r="M10" s="4"/>
       <c r="N10" s="2"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
@@ -12337,9 +12418,10 @@
       <c r="L11" s="1"/>
       <c r="M11" s="4"/>
       <c r="N11" s="2"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -12358,9 +12440,10 @@
       <c r="L12" s="1"/>
       <c r="M12" s="4"/>
       <c r="N12" s="2"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
@@ -12379,9 +12462,10 @@
       <c r="L13" s="1"/>
       <c r="M13" s="4"/>
       <c r="N13" s="2"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
@@ -12400,9 +12484,10 @@
       <c r="L14" s="1"/>
       <c r="M14" s="4"/>
       <c r="N14" s="2"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
@@ -12421,9 +12506,10 @@
       <c r="L15" s="1"/>
       <c r="M15" s="4"/>
       <c r="N15" s="2"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
@@ -12442,9 +12528,10 @@
       <c r="L16" s="1"/>
       <c r="M16" s="4"/>
       <c r="N16" s="2"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
@@ -12463,9 +12550,10 @@
       <c r="L17" s="1"/>
       <c r="M17" s="4"/>
       <c r="N17" s="2"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
@@ -12484,9 +12572,10 @@
       <c r="L18" s="6"/>
       <c r="M18" s="4"/>
       <c r="N18" s="2"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
@@ -12505,9 +12594,10 @@
       <c r="L19" s="6"/>
       <c r="M19" s="4"/>
       <c r="N19" s="2"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
@@ -12526,9 +12616,10 @@
       <c r="L20" s="6"/>
       <c r="M20" s="4"/>
       <c r="N20" s="2"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
@@ -12547,9 +12638,10 @@
       <c r="L21" s="6"/>
       <c r="M21" s="4"/>
       <c r="N21" s="2"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
@@ -12568,9 +12660,10 @@
       <c r="L22" s="6"/>
       <c r="M22" s="4"/>
       <c r="N22" s="2"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
@@ -12659,6 +12752,9 @@
       <c r="L27" s="6"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O3" r:id="rId1" display="https://ibb.co.com/qMZNjg2v " xr:uid="{52187821-6BE5-4690-9EC5-C5CCF475DB69}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695EDDD4-F558-44E9-A2C3-D7A2A1931FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C57E37-73BB-4AC3-B0C0-9DA8CEC37F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="143">
   <si>
     <t>model</t>
   </si>
@@ -473,6 +473,33 @@
 https://ibb.co.com/zTrKmB47
 https://ibb.co.com/gMdqw04Q</t>
   </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>100339_1 100339_2 100339_3 100339_4 100339_5 100339_6</t>
+  </si>
+  <si>
+    <t>10,5c</t>
+  </si>
+  <si>
+    <t>Nike Revolution 6 Next Nature (PSV) DD1095-608 — детские кроссовки для повседневной носки и лёгкого бега; лёгкий текстильный верх обеспечивает воздухопроницаемость и комфорт; мягкая пенная подошва даёт амортизацию при каждом шаге; резиновая подмётка гарантирует надёжное сцепление; эластичные шнурки и липучка обеспечивают удобное надевание и фиксацию; усиленный носок повышает износостойкость; модель содержит не менее 20% переработанных материалов.</t>
+  </si>
+  <si>
+    <t>girls</t>
+  </si>
+  <si>
+    <t>Revolution 6 NN (PSV)</t>
+  </si>
+  <si>
+    <t>100340_1 100340_2 100340_3 100340_4 100340_5 100340_6</t>
+  </si>
+  <si>
+    <t>12,5c</t>
+  </si>
+  <si>
+    <t>100341_1 100341_2 100341_3 100341_4 100341_5 100341_6</t>
+  </si>
 </sst>
 </file>
 
@@ -584,7 +611,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,10 +659,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -10228,7 +10251,7 @@
       </c>
       <c r="L287" s="1"/>
       <c r="M287" s="4">
-        <f t="shared" ref="M287:M339" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
+        <f t="shared" ref="M287:M342" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
         <v>74033.421052631587</v>
       </c>
       <c r="N287" s="2">
@@ -10379,7 +10402,7 @@
         <v>44</v>
       </c>
       <c r="I292" s="5">
-        <f t="shared" ref="I292:I339" si="14">M292</f>
+        <f t="shared" ref="I292:I342" si="14">M292</f>
         <v>74830.789473684214</v>
       </c>
       <c r="J292" s="1"/>
@@ -11850,7 +11873,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="337" spans="1:15" ht="102" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:15" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A337" s="1">
         <v>100336</v>
       </c>
@@ -11971,22 +11994,133 @@
       </c>
     </row>
     <row r="340" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A340" s="15">
+      <c r="A340" s="1">
         <v>100339</v>
+      </c>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H340" s="1">
+        <v>27.5</v>
+      </c>
+      <c r="I340" s="1">
+        <f t="shared" si="14"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="J340" s="1"/>
+      <c r="K340" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L340" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M340" s="2">
+        <f t="shared" si="13"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="N340" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
         <v>100340</v>
       </c>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F341" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G341" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H341" s="1">
+        <v>30</v>
+      </c>
+      <c r="I341" s="1">
+        <f t="shared" si="14"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="J341" s="1"/>
+      <c r="K341" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L341" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M341" s="2">
+        <f t="shared" si="13"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="N341" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="342" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
         <v>100341</v>
       </c>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G342" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="H342" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="I342" s="1">
+        <f t="shared" si="14"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="J342" s="1"/>
+      <c r="K342" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L342" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M342" s="2">
+        <f t="shared" si="13"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="N342" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A343" s="1">
+      <c r="A343" s="15">
         <v>100342</v>
       </c>
     </row>
@@ -12243,9 +12377,9 @@
       <c r="O3" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
@@ -12264,10 +12398,9 @@
       <c r="L4" s="1"/>
       <c r="M4" s="4"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
@@ -12286,10 +12419,9 @@
       <c r="L5" s="1"/>
       <c r="M5" s="4"/>
       <c r="N5" s="2"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
@@ -12308,10 +12440,9 @@
       <c r="L6" s="1"/>
       <c r="M6" s="4"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
@@ -12330,10 +12461,9 @@
       <c r="L7" s="1"/>
       <c r="M7" s="4"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
@@ -12352,10 +12482,9 @@
       <c r="L8" s="1"/>
       <c r="M8" s="4"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
@@ -12374,10 +12503,9 @@
       <c r="L9" s="1"/>
       <c r="M9" s="4"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
@@ -12396,10 +12524,9 @@
       <c r="L10" s="1"/>
       <c r="M10" s="4"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
@@ -12418,10 +12545,9 @@
       <c r="L11" s="1"/>
       <c r="M11" s="4"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -12440,10 +12566,9 @@
       <c r="L12" s="1"/>
       <c r="M12" s="4"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
@@ -12462,10 +12587,9 @@
       <c r="L13" s="1"/>
       <c r="M13" s="4"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
@@ -12484,10 +12608,9 @@
       <c r="L14" s="1"/>
       <c r="M14" s="4"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
@@ -12506,10 +12629,9 @@
       <c r="L15" s="1"/>
       <c r="M15" s="4"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
@@ -12528,10 +12650,9 @@
       <c r="L16" s="1"/>
       <c r="M16" s="4"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
@@ -12550,10 +12671,9 @@
       <c r="L17" s="1"/>
       <c r="M17" s="4"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
@@ -12572,10 +12692,9 @@
       <c r="L18" s="6"/>
       <c r="M18" s="4"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
@@ -12594,10 +12713,9 @@
       <c r="L19" s="6"/>
       <c r="M19" s="4"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
@@ -12616,10 +12734,9 @@
       <c r="L20" s="6"/>
       <c r="M20" s="4"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
@@ -12638,10 +12755,9 @@
       <c r="L21" s="6"/>
       <c r="M21" s="4"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
@@ -12660,10 +12776,9 @@
       <c r="L22" s="6"/>
       <c r="M22" s="4"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="1">

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C57E37-73BB-4AC3-B0C0-9DA8CEC37F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22365C29-7DBD-4566-AD66-8793F5086843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="145">
   <si>
     <t>model</t>
   </si>
@@ -499,6 +499,22 @@
   </si>
   <si>
     <t>100341_1 100341_2 100341_3 100341_4 100341_5 100341_6</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/Rky7vx2r
+https://ibb.co.com/mC5NWGsd
+https://ibb.co.com/k2R0SQWZ
+https://ibb.co.com/MDMVPzfn
+https://ibb.co.com/spgKpjVP
+https://ibb.co.com/XxszYJjz</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/9mBN1Bc8
+https://ibb.co.com/gFhrBvPj
+https://ibb.co.com/Bk0BwdN
+https://ibb.co.com/0pQ4fGFG
+https://ibb.co.com/mVNkB4HR
+https://ibb.co.com/0pMvccCB</t>
   </si>
 </sst>
 </file>
@@ -11993,7 +12009,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:15" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A340" s="1">
         <v>100339</v>
       </c>
@@ -12034,8 +12050,11 @@
       <c r="N340" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O340" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
         <v>100340</v>
       </c>
@@ -12076,8 +12095,11 @@
       <c r="N341" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O341" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
         <v>100341</v>
       </c>
@@ -12117,6 +12139,9 @@
       </c>
       <c r="N342" s="2">
         <v>1</v>
+      </c>
+      <c r="O342" s="14" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.4">

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22365C29-7DBD-4566-AD66-8793F5086843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8491E7A-F85F-4DA5-B878-CF38C2F13AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="145">
   <si>
     <t>model</t>
   </si>
@@ -489,9 +489,6 @@
     <t>girls</t>
   </si>
   <si>
-    <t>Revolution 6 NN (PSV)</t>
-  </si>
-  <si>
     <t>100340_1 100340_2 100340_3 100340_4 100340_5 100340_6</t>
   </si>
   <si>
@@ -515,6 +512,9 @@
 https://ibb.co.com/0pQ4fGFG
 https://ibb.co.com/mVNkB4HR
 https://ibb.co.com/0pMvccCB</t>
+  </si>
+  <si>
+    <t>Revolution 6 NN PSV</t>
   </si>
 </sst>
 </file>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B340" s="1"/>
       <c r="C340" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>138</v>
@@ -12051,7 +12051,7 @@
         <v>1</v>
       </c>
       <c r="O340" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="341" spans="1:15" ht="87.45" x14ac:dyDescent="0.4">
@@ -12059,9 +12059,7 @@
         <v>100340</v>
       </c>
       <c r="B341" s="1"/>
-      <c r="C341" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="C341" s="1"/>
       <c r="D341" s="1" t="s">
         <v>113</v>
       </c>
@@ -12069,10 +12067,10 @@
         <v>43</v>
       </c>
       <c r="F341" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G341" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="G341" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="H341" s="1">
         <v>30</v>
@@ -12104,9 +12102,7 @@
         <v>100341</v>
       </c>
       <c r="B342" s="1"/>
-      <c r="C342" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="C342" s="1"/>
       <c r="D342" s="1" t="s">
         <v>113</v>
       </c>
@@ -12114,7 +12110,7 @@
         <v>86</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G342" s="1">
         <v>13.5</v>
@@ -12141,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="O342" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.4">

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8491E7A-F85F-4DA5-B878-CF38C2F13AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2702AAA-C54B-43D8-BE44-8055E64D6F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="146">
   <si>
     <t>model</t>
   </si>
@@ -483,9 +483,6 @@
     <t>10,5c</t>
   </si>
   <si>
-    <t>Nike Revolution 6 Next Nature (PSV) DD1095-608 — детские кроссовки для повседневной носки и лёгкого бега; лёгкий текстильный верх обеспечивает воздухопроницаемость и комфорт; мягкая пенная подошва даёт амортизацию при каждом шаге; резиновая подмётка гарантирует надёжное сцепление; эластичные шнурки и липучка обеспечивают удобное надевание и фиксацию; усиленный носок повышает износостойкость; модель содержит не менее 20% переработанных материалов.</t>
-  </si>
-  <si>
     <t>girls</t>
   </si>
   <si>
@@ -515,6 +512,12 @@
   </si>
   <si>
     <t>Revolution 6 NN PSV</t>
+  </si>
+  <si>
+    <t>13,5c</t>
+  </si>
+  <si>
+    <t>Nike Revolution 6 Next Nature — детские кроссовки для повседневной носки и лёгкого бега; лёгкий текстильный верх обеспечивает воздухопроницаемость и комфорт; мягкая пенная подошва даёт амортизацию при каждом шаге; резиновая подмётка гарантирует надёжное сцепление; эластичные шнурки и липучка обеспечивают удобное надевание и фиксацию; усиленный носок повышает износостойкость; модель содержит не менее 20% переработанных материалов.</t>
   </si>
 </sst>
 </file>
@@ -12015,10 +12018,10 @@
       </c>
       <c r="B340" s="1"/>
       <c r="C340" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>134</v>
@@ -12041,7 +12044,7 @@
         <v>25</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M340" s="2">
         <f t="shared" si="13"/>
@@ -12051,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="O340" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="341" spans="1:15" ht="87.45" x14ac:dyDescent="0.4">
@@ -12067,10 +12070,10 @@
         <v>43</v>
       </c>
       <c r="F341" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G341" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="G341" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="H341" s="1">
         <v>30</v>
@@ -12084,7 +12087,7 @@
         <v>25</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M341" s="2">
         <f t="shared" si="13"/>
@@ -12110,10 +12113,10 @@
         <v>86</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G342" s="1">
-        <v>13.5</v>
+        <v>140</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="H342" s="1">
         <v>31.5</v>
@@ -12127,7 +12130,7 @@
         <v>25</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M342" s="2">
         <f t="shared" si="13"/>
@@ -12137,7 +12140,7 @@
         <v>1</v>
       </c>
       <c r="O342" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.4">

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2702AAA-C54B-43D8-BE44-8055E64D6F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BCD9AA-3577-48AB-B26B-548F31E04C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="150">
   <si>
     <t>model</t>
   </si>
@@ -518,6 +518,22 @@
   </si>
   <si>
     <t>Nike Revolution 6 Next Nature — детские кроссовки для повседневной носки и лёгкого бега; лёгкий текстильный верх обеспечивает воздухопроницаемость и комфорт; мягкая пенная подошва даёт амортизацию при каждом шаге; резиновая подмётка гарантирует надёжное сцепление; эластичные шнурки и липучка обеспечивают удобное надевание и фиксацию; усиленный носок повышает износостойкость; модель содержит не менее 20% переработанных материалов.</t>
+  </si>
+  <si>
+    <t>Downshifter 10 PSV</t>
+  </si>
+  <si>
+    <t>100342_1 100342_2 100342_3 100342_4 100342_5</t>
+  </si>
+  <si>
+    <t>Nike Downshifter 10 (PSV) — детские кроссовки для повседневной носки и лёгкого бега; верх из дышащей сетки с синтетическими накладками обеспечивает вентиляцию и поддержку; усиленная зона средней части стопы и мягкая пятка дают надёжную фиксацию и комфорт; лёгкая пенная промежуточная подошва (Phylon) обеспечивает амортизацию и гибкость при движении; резиновая подмётка с разделённой конструкцией и гибкими канавками улучшает сцепление, устойчивость и естественность шага.</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/sd1qZZ7j
+https://ibb.co.com/QFTNdtyj
+https://ibb.co.com/CK0LgnKv
+https://ibb.co.com/0VQP1wgj
+https://ibb.co.com/6cGWdtv7</t>
   </si>
 </sst>
 </file>
@@ -10270,7 +10286,7 @@
       </c>
       <c r="L287" s="1"/>
       <c r="M287" s="4">
-        <f t="shared" ref="M287:M342" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
+        <f t="shared" ref="M287:M343" si="13">(N287*75+N287*75*0.01+15000+4200+5000)/0.95</f>
         <v>74033.421052631587</v>
       </c>
       <c r="N287" s="2">
@@ -10421,7 +10437,7 @@
         <v>44</v>
       </c>
       <c r="I292" s="5">
-        <f t="shared" ref="I292:I342" si="14">M292</f>
+        <f t="shared" ref="I292:I343" si="14">M292</f>
         <v>74830.789473684214</v>
       </c>
       <c r="J292" s="1"/>
@@ -12143,13 +12159,53 @@
         <v>142</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A343" s="15">
+    <row r="343" spans="1:15" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A343" s="1">
         <v>100342</v>
       </c>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F343" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G343" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H343" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="I343" s="1">
+        <f t="shared" si="14"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="J343" s="1"/>
+      <c r="K343" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L343" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="M343" s="2">
+        <f t="shared" si="13"/>
+        <v>25553.42105263158</v>
+      </c>
+      <c r="N343" s="2">
+        <v>1</v>
+      </c>
+      <c r="O343" s="14" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A344" s="1">
+      <c r="A344" s="15">
         <v>100343</v>
       </c>
     </row>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BCD9AA-3577-48AB-B26B-548F31E04C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D2CCA-BBB7-4847-B132-2622CC28C598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="11143" windowHeight="11709" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="153">
   <si>
     <t>model</t>
   </si>
@@ -535,6 +535,15 @@
 https://ibb.co.com/0VQP1wgj
 https://ibb.co.com/6cGWdtv7</t>
   </si>
+  <si>
+    <t>Terrex Ax4 Gore-Tex Hiking</t>
+  </si>
+  <si>
+    <t>900011_1 900011_2 900011_3 900011_4 900011_5 900011_6</t>
+  </si>
+  <si>
+    <t>Adidas Terrex AX4 GORE-TEX — универсальные трекинговые кроссовки для походов и активного отдыха; лёгкий верх из сетки и синтетических материалов обеспечивает прочность и вентиляцию; мембрана GORE-TEX защищает от влаги и сохраняет ноги сухими в дождливых условиях; промежуточная подошва из EVA даёт амортизацию и комфорт при длительной ходьбе; подошва из резины Continental™ обеспечивает отличное сцепление на сухих и мокрых поверхностях; модель сочетает лёгкость беговых кроссовок с устойчивостью трекинговой обуви и выполнена с использованием переработанных материалов Primegreen</t>
+  </si>
 </sst>
 </file>
 
@@ -15665,7 +15674,7 @@
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="4">
-        <f t="shared" ref="M3:M11" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
+        <f t="shared" ref="M3:M12" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
         <v>43812.368421052633</v>
       </c>
       <c r="N3" s="2">
@@ -15935,18 +15944,42 @@
         <v>900011</v>
       </c>
       <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="5"/>
+      <c r="C12" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>44</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" ref="I12" si="2">M12</f>
+        <v>65341.315789473687</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="2"/>
+      <c r="K12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>152</v>
+      </c>
+      <c r="M12" s="4">
+        <f t="shared" si="1"/>
+        <v>65341.315789473687</v>
+      </c>
+      <c r="N12" s="2">
+        <v>599</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="1">

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\jmd_store_render\jmd_store\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D2CCA-BBB7-4847-B132-2622CC28C598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B332B3-B119-4E7E-A3DD-BC54F60B6224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="11143" windowHeight="11709" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nike" sheetId="3" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Dickies" sheetId="13" r:id="rId8"/>
     <sheet name="Skechers" sheetId="14" r:id="rId9"/>
     <sheet name="Asics" sheetId="16" r:id="rId10"/>
+    <sheet name="Puma" sheetId="18" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="159">
   <si>
     <t>model</t>
   </si>
@@ -544,6 +545,33 @@
   <si>
     <t>Adidas Terrex AX4 GORE-TEX — универсальные трекинговые кроссовки для походов и активного отдыха; лёгкий верх из сетки и синтетических материалов обеспечивает прочность и вентиляцию; мембрана GORE-TEX защищает от влаги и сохраняет ноги сухими в дождливых условиях; промежуточная подошва из EVA даёт амортизацию и комфорт при длительной ходьбе; подошва из резины Continental™ обеспечивает отличное сцепление на сухих и мокрых поверхностях; модель сочетает лёгкость беговых кроссовок с устойчивостью трекинговой обуви и выполнена с использованием переработанных материалов Primegreen</t>
   </si>
+  <si>
+    <t>https://ibb.co.com/pBvvVsbN
+https://ibb.co.com/hxDDXnJL
+https://ibb.co.com/B23xrJjH
+https://ibb.co.com/yn8FtD5J
+https://ibb.co.com/84BQcc3d
+https://ibb.co.com/qL32pDwr</t>
+  </si>
+  <si>
+    <t>Puma</t>
+  </si>
+  <si>
+    <t>Smash SD</t>
+  </si>
+  <si>
+    <t>140001_1 140001_2 140001_3 140001_4 140001_5</t>
+  </si>
+  <si>
+    <t>Puma Smash SD — классические кеды в теннисном стиле для повседневной носки; верх выполнен из мягкой замши (suede), обеспечивающей комфорт и премиальный внешний вид; низкий силуэт и шнуровка дают удобную посадку и фиксацию; прочная резиновая подошва обеспечивает надёжное сцепление и износостойкость; текстильная подкладка улучшает вентиляцию и комфорт при длительном ношении; универсальный дизайн в стиле court подходит под любой повседневный образ.</t>
+  </si>
+  <si>
+    <t>https://ibb.co.com/Zzw48yjZ
+https://ibb.co.com/4vzPq3p
+https://ibb.co.com/ks1yFhHK
+https://ibb.co.com/gL3mhLCd
+https://ibb.co.com/DDtv25pb</t>
+  </si>
 </sst>
 </file>
 
@@ -655,7 +683,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -703,6 +731,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -12372,7 +12401,7 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:18" ht="291.45" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" ht="66.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>130001</v>
       </c>
@@ -12422,7 +12451,7 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18" ht="291.45" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="50.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>130002</v>
       </c>
@@ -12959,6 +12988,445 @@
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" display="https://ibb.co.com/qMZNjg2v " xr:uid="{52187821-6BE5-4690-9EC5-C5CCF475DB69}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9B43DC-1EEE-45E0-88D2-2722F7C5B040}">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="15.15234375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.23046875" style="2"/>
+    <col min="12" max="12" width="76.07421875" customWidth="1"/>
+    <col min="15" max="15" width="27.4609375" customWidth="1"/>
+    <col min="16" max="16" width="25.765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A2" s="1">
+        <v>140001</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>37</v>
+      </c>
+      <c r="I2" s="5">
+        <f>M2</f>
+        <v>35599.473684210527</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M2" s="4">
+        <f>(N2*75+N2*75*0.01+12500+4200)/0.95</f>
+        <v>35599.473684210527</v>
+      </c>
+      <c r="N2" s="2">
+        <v>226</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A3" s="1">
+        <v>140002</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="5">
+        <f t="shared" ref="I3:I9" si="0">M3</f>
+        <v>43812.368421052633</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="4">
+        <f t="shared" ref="M3:M12" si="1">(N3*75+N3*75*0.01+12500+4200)/0.95</f>
+        <v>43812.368421052633</v>
+      </c>
+      <c r="N3" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>140003</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>44609.736842105267</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="4">
+        <f t="shared" si="1"/>
+        <v>44609.736842105267</v>
+      </c>
+      <c r="N4" s="2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
+        <v>140004</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="5">
+        <f t="shared" si="0"/>
+        <v>43812.368421052633</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="4">
+        <f t="shared" si="1"/>
+        <v>43812.368421052633</v>
+      </c>
+      <c r="N5" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>140005</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>45407.1052631579</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="4">
+        <f t="shared" si="1"/>
+        <v>45407.1052631579</v>
+      </c>
+      <c r="N6" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>140006</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>47799.210526315794</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="4">
+        <f t="shared" si="1"/>
+        <v>47799.210526315794</v>
+      </c>
+      <c r="N7" s="2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A8" s="1">
+        <v>140007</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>49393.947368421053</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="4">
+        <f t="shared" si="1"/>
+        <v>49393.947368421053</v>
+      </c>
+      <c r="N8" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A9" s="1">
+        <v>140008</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>48596.57894736842</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="4">
+        <f t="shared" si="1"/>
+        <v>48596.57894736842</v>
+      </c>
+      <c r="N9" s="2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A10" s="1">
+        <v>140009</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="4">
+        <f t="shared" si="1"/>
+        <v>97236.052631578947</v>
+      </c>
+      <c r="N10" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A11" s="1">
+        <v>140010</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A12" s="1">
+        <v>140011</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="8"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A13" s="1">
+        <v>140012</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="2"/>
+      <c r="P13" s="17"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A14" s="1">
+        <v>140013</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A15" s="1">
+        <v>140014</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
+        <v>140015</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A17" s="1">
+        <v>140016</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15557,7 +16025,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B19D1D-483E-48F2-ADAB-DFF52736FC78}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="15.15234375" bestFit="1" customWidth="1"/>
@@ -15565,9 +16033,11 @@
     <col min="6" max="6" width="60.53515625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9.23046875" style="2"/>
     <col min="12" max="12" width="76.07421875" customWidth="1"/>
+    <col min="15" max="15" width="27.4609375" customWidth="1"/>
+    <col min="16" max="16" width="25.765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -15607,7 +16077,7 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>900001</v>
       </c>
@@ -15649,7 +16119,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>900002</v>
       </c>
@@ -15681,7 +16151,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>900003</v>
       </c>
@@ -15713,7 +16183,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>900004</v>
       </c>
@@ -15745,7 +16215,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>900005</v>
       </c>
@@ -15777,7 +16247,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>900006</v>
       </c>
@@ -15809,7 +16279,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>900007</v>
       </c>
@@ -15841,7 +16311,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>900008</v>
       </c>
@@ -15873,7 +16343,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>900009</v>
       </c>
@@ -15898,7 +16368,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>900010</v>
       </c>
@@ -15939,7 +16409,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>900011</v>
       </c>
@@ -15980,8 +16450,11 @@
       <c r="N12" s="2">
         <v>599</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O12" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>900012</v>
       </c>
@@ -15998,8 +16471,9 @@
       <c r="L13" s="6"/>
       <c r="M13" s="4"/>
       <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P13" s="17"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>900013</v>
       </c>
@@ -16017,7 +16491,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>900014</v>
       </c>
@@ -16035,7 +16509,7 @@
       <c r="M15" s="4"/>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>900015</v>
       </c>
